--- a/Etapa Construcción - Iteración 1/Estimación 04 Caso Más Probable - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Estimación 04 Caso Más Probable - Kairos - NexTech.xlsx
@@ -1068,7 +1068,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1257,7 +1257,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1297,6 +1297,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4395,12 +4398,12 @@
       </c>
       <c r="D71" s="64">
         <f>IF($G$64&gt;=5,$G$71*(36/20),IF(AND($G$64&gt;2,$G$64&lt;=4),$G$71*(28/20), IF(AND($G$64&gt;=0,$G$64&lt;=2),$G$71,"error")))</f>
-        <v>2.8</v>
+        <v>4.382</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="1"/>
       <c r="G71" s="65">
-        <v>2.0</v>
+        <v>3.13</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -4466,7 +4469,7 @@
       </c>
       <c r="D73" s="63">
         <f t="shared" si="9"/>
-        <v>324.04736</v>
+        <v>507.1341184</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="1"/>
@@ -4505,7 +4508,7 @@
       </c>
       <c r="D74" s="69">
         <f>D73/(22*3)</f>
-        <v>4.909808485</v>
+        <v>7.683850279</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="1"/>
@@ -4674,7 +4677,7 @@
       </c>
       <c r="F79" s="68">
         <f t="shared" si="11"/>
-        <v>4.909808485</v>
+        <v>7.683850279</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -4716,7 +4719,7 @@
       </c>
       <c r="F80" s="63">
         <f t="shared" si="12"/>
-        <v>7.364712727</v>
+        <v>11.52577542</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -4756,7 +4759,7 @@
       </c>
       <c r="F81" s="68">
         <f t="shared" si="13"/>
-        <v>12.27452121</v>
+        <v>19.2096257</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -4915,7 +4918,7 @@
       </c>
       <c r="D86" s="77">
         <f>$F$81/$B$83</f>
-        <v>2.454904242</v>
+        <v>3.841925139</v>
       </c>
       <c r="E86" s="76"/>
       <c r="F86" s="76"/>
@@ -13858,7 +13861,7 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="65">
+      <c r="G71" s="79">
         <v>2.0</v>
       </c>
       <c r="H71" s="1"/>
@@ -20714,16 +20717,16 @@
     <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B49:F49"/>
   </mergeCells>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C8:C11">

--- a/Etapa Construcción - Iteración 1/Estimación 04 Caso Más Probable - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Estimación 04 Caso Más Probable - Kairos - NexTech.xlsx
@@ -4398,12 +4398,12 @@
       </c>
       <c r="D71" s="64">
         <f>IF($G$64&gt;=5,$G$71*(36/20),IF(AND($G$64&gt;2,$G$64&lt;=4),$G$71*(28/20), IF(AND($G$64&gt;=0,$G$64&lt;=2),$G$71,"error")))</f>
-        <v>4.382</v>
+        <v>2.8</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="1"/>
       <c r="G71" s="65">
-        <v>3.13</v>
+        <v>2.0</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D73" s="63">
         <f t="shared" si="9"/>
-        <v>507.1341184</v>
+        <v>324.04736</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="1"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="D74" s="69">
         <f>D73/(22*3)</f>
-        <v>7.683850279</v>
+        <v>4.909808485</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="1"/>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="F79" s="68">
         <f t="shared" si="11"/>
-        <v>7.683850279</v>
+        <v>4.909808485</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F80" s="63">
         <f t="shared" si="12"/>
-        <v>11.52577542</v>
+        <v>7.364712727</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="F81" s="68">
         <f t="shared" si="13"/>
-        <v>19.2096257</v>
+        <v>12.27452121</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D86" s="77">
         <f>$F$81/$B$83</f>
-        <v>3.841925139</v>
+        <v>2.454904242</v>
       </c>
       <c r="E86" s="76"/>
       <c r="F86" s="76"/>

--- a/Etapa Construcción - Iteración 1/Estimación 04 Caso Más Probable - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Estimación 04 Caso Más Probable - Kairos - NexTech.xlsx
@@ -270,7 +270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="138">
   <si>
     <t>ESTIMACIÓN por PUNTOS de CASO de USO</t>
   </si>
@@ -323,15 +323,6 @@
     <t>Usuario con acceso a vistas</t>
   </si>
   <si>
-    <t>Toggl Track</t>
-  </si>
-  <si>
-    <t>Simple</t>
-  </si>
-  <si>
-    <t>Otro sistema con una API</t>
-  </si>
-  <si>
     <t>Miembro</t>
   </si>
   <si>
@@ -356,22 +347,19 @@
     <t>Complejidad</t>
   </si>
   <si>
-    <t>CU23: Registrar usuario a proyecto</t>
+    <t>CU07: Crear etapa</t>
   </si>
   <si>
-    <t>CU05: Crear Proyecto</t>
+    <t>Simple</t>
+  </si>
+  <si>
+    <t>CU23: Registrar usuario a proyecto</t>
   </si>
   <si>
     <t>CU##: Gestionar proyectos</t>
   </si>
   <si>
-    <t>CU08: Crear iteracion</t>
-  </si>
-  <si>
-    <t>CU07: Crear etapa</t>
-  </si>
-  <si>
-    <t>CU##: Gestionar iteraciones</t>
+    <t>CU08: Crear iteración</t>
   </si>
   <si>
     <t>CU##: Gestionar tareas</t>
@@ -745,6 +733,21 @@
 (m)</t>
   </si>
   <si>
+    <t>Toggl Track</t>
+  </si>
+  <si>
+    <t>Otro sistema con una API</t>
+  </si>
+  <si>
+    <t>CU05: Crear Proyecto</t>
+  </si>
+  <si>
+    <t>CU08: Crear iteracion</t>
+  </si>
+  <si>
+    <t>CU##: Gestionar iteraciones</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <rFont val="Calibri"/>
@@ -834,7 +837,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -875,6 +878,10 @@
       <sz val="12.0"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -1068,7 +1075,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="92">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1170,17 +1177,46 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1211,10 +1247,10 @@
     <xf borderId="9" fillId="3" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1247,7 +1283,7 @@
     <xf borderId="9" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="15" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1283,7 +1319,7 @@
     <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="11" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="3" fontId="12" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1297,6 +1333,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="9" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2154,24 +2193,12 @@
     </row>
     <row r="10" ht="27.75" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="24">
-        <v>1.0</v>
-      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -2195,13 +2222,13 @@
     <row r="11" ht="27.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="21" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E11" s="24">
         <f>IF(C11="Simple",1,IF(C11="Intermedio",2,IF(C11="Complejo",3,"error")))</f>
@@ -2237,14 +2264,14 @@
       <c r="A12" s="1"/>
       <c r="B12" s="28"/>
       <c r="C12" s="29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
       <c r="G12" s="30">
         <f>SUM(G8:G11)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2324,19 +2351,19 @@
     </row>
     <row r="15" ht="27.75" customHeight="1">
       <c r="A15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>27</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>9</v>
@@ -2364,26 +2391,24 @@
     </row>
     <row r="16" ht="27.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="35">
-        <v>6.0</v>
-      </c>
-      <c r="E16" s="24" t="str">
-        <f t="shared" ref="E16:E18" si="1">IF($D16&gt;0,IF($D16&lt;=3,"Simple",IF(AND($D16&gt;3,$D16&lt;7),"Intermedio",IF($D16&gt;=7,"Complejo","error"))),"-")</f>
-        <v>Intermedio</v>
-      </c>
-      <c r="F16" s="24">
-        <f t="shared" ref="F16:F18" si="2">IF($D16&gt;0,IF($D16&lt;=3,5,IF(AND($D16&gt;3,$D16&lt;7),10,IF($D16&gt;=7,15,"error"))),0)</f>
-        <v>10</v>
+      <c r="B16" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37">
+        <v>3.0</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="38">
+        <v>5.0</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="36"/>
+      <c r="K16" s="39"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -2392,7 +2417,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="36"/>
+      <c r="T16" s="39"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -2402,26 +2427,26 @@
     </row>
     <row r="17" ht="27.75" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="35">
-        <v>2.0</v>
-      </c>
-      <c r="E17" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>Simple</v>
-      </c>
-      <c r="F17" s="24">
-        <f t="shared" si="2"/>
-        <v>5</v>
+      <c r="B17" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E17" s="43" t="str">
+        <f t="shared" ref="E17:E18" si="1">IF($D17&gt;0,IF($D17&lt;=3,"Simple",IF(AND($D17&gt;3,$D17&lt;7),"Intermedio",IF($D17&gt;=7,"Complejo","error"))),"-")</f>
+        <v>Intermedio</v>
+      </c>
+      <c r="F17" s="43">
+        <f t="shared" ref="F17:F18" si="2">IF($D17&gt;0,IF($D17&lt;=3,5,IF(AND($D17&gt;3,$D17&lt;7),10,IF($D17&gt;=7,15,"error"))),0)</f>
+        <v>10</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="36"/>
+      <c r="K17" s="39"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -2430,7 +2455,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="36"/>
+      <c r="T17" s="39"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -2440,26 +2465,26 @@
     </row>
     <row r="18" ht="27.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38">
-        <v>6.0</v>
-      </c>
-      <c r="E18" s="24" t="str">
+      <c r="B18" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45">
+        <v>8.0</v>
+      </c>
+      <c r="E18" s="43" t="str">
         <f t="shared" si="1"/>
-        <v>Intermedio</v>
-      </c>
-      <c r="F18" s="24">
+        <v>Complejo</v>
+      </c>
+      <c r="F18" s="43">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="36"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2468,7 +2493,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="36"/>
+      <c r="T18" s="39"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -2478,24 +2503,24 @@
     </row>
     <row r="19" ht="27.75" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38">
+      <c r="B19" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="46">
         <v>3.0</v>
       </c>
-      <c r="E19" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="24">
+      <c r="E19" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="43">
         <v>5.0</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="36"/>
+      <c r="K19" s="39"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2504,7 +2529,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="36"/>
+      <c r="T19" s="39"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -2514,26 +2539,26 @@
     </row>
     <row r="20" ht="27.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E20" s="24" t="str">
-        <f t="shared" ref="E20:E22" si="3">IF($D20&gt;0,IF($D20&lt;=3,"Simple",IF(AND($D20&gt;3,$D20&lt;7),"Intermedio",IF($D20&gt;=7,"Complejo","error"))),"-")</f>
-        <v>Simple</v>
-      </c>
-      <c r="F20" s="24">
-        <f t="shared" ref="F20:F22" si="4">IF($D20&gt;0,IF($D20&lt;=3,5,IF(AND($D20&gt;3,$D20&lt;7),10,IF($D20&gt;=7,15,"error"))),0)</f>
-        <v>5</v>
+      <c r="B20" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="44"/>
+      <c r="D20" s="46">
+        <v>10.0</v>
+      </c>
+      <c r="E20" s="43" t="str">
+        <f>IF($D20&gt;0,IF($D20&lt;=3,"Simple",IF(AND($D20&gt;3,$D20&lt;7),"Intermedio",IF($D20&gt;=7,"Complejo","error"))),"-")</f>
+        <v>Complejo</v>
+      </c>
+      <c r="F20" s="43">
+        <f>IF($D20&gt;0,IF($D20&lt;=3,5,IF(AND($D20&gt;3,$D20&lt;7),10,IF($D20&gt;=7,15,"error"))),0)</f>
+        <v>15</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="36"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -2542,7 +2567,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="36"/>
+      <c r="T20" s="39"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
@@ -2552,26 +2577,24 @@
     </row>
     <row r="21" ht="27.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v>Simple</v>
-      </c>
-      <c r="F21" s="24">
-        <f t="shared" si="4"/>
-        <v>5</v>
+      <c r="B21" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="44"/>
+      <c r="D21" s="45">
+        <v>4.0</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="43">
+        <v>10.0</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="36"/>
+      <c r="K21" s="39"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2580,7 +2603,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="36"/>
+      <c r="T21" s="39"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
@@ -2590,26 +2613,26 @@
     </row>
     <row r="22" ht="27.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38">
-        <v>10.0</v>
-      </c>
-      <c r="E22" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v>Complejo</v>
-      </c>
-      <c r="F22" s="24">
-        <f t="shared" si="4"/>
-        <v>15</v>
+      <c r="B22" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="44"/>
+      <c r="D22" s="46">
+        <v>4.0</v>
+      </c>
+      <c r="E22" s="43" t="str">
+        <f t="shared" ref="E22:E26" si="3">IF($D22&gt;0,IF($D22&lt;=3,"Simple",IF(AND($D22&gt;3,$D22&lt;7),"Intermedio",IF($D22&gt;=7,"Complejo","error"))),"-")</f>
+        <v>Intermedio</v>
+      </c>
+      <c r="F22" s="43">
+        <f t="shared" ref="F22:F26" si="4">IF($D22&gt;0,IF($D22&lt;=3,5,IF(AND($D22&gt;3,$D22&lt;7),10,IF($D22&gt;=7,15,"error"))),0)</f>
+        <v>10</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="36"/>
+      <c r="K22" s="39"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -2618,7 +2641,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="36"/>
+      <c r="T22" s="39"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -2628,24 +2651,26 @@
     </row>
     <row r="23" ht="27.75" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38">
-        <v>4.0</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="24">
-        <v>10.0</v>
+      <c r="B23" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="44"/>
+      <c r="D23" s="46">
+        <v>3.0</v>
+      </c>
+      <c r="E23" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>Simple</v>
+      </c>
+      <c r="F23" s="43">
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="36"/>
+      <c r="K23" s="39"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2654,7 +2679,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="36"/>
+      <c r="T23" s="39"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -2664,26 +2689,26 @@
     </row>
     <row r="24" ht="27.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38">
-        <v>4.0</v>
-      </c>
-      <c r="E24" s="24" t="str">
-        <f t="shared" ref="E24:E28" si="5">IF($D24&gt;0,IF($D24&lt;=3,"Simple",IF(AND($D24&gt;3,$D24&lt;7),"Intermedio",IF($D24&gt;=7,"Complejo","error"))),"-")</f>
-        <v>Intermedio</v>
-      </c>
-      <c r="F24" s="24">
-        <f t="shared" ref="F24:F28" si="6">IF($D24&gt;0,IF($D24&lt;=3,5,IF(AND($D24&gt;3,$D24&lt;7),10,IF($D24&gt;=7,15,"error"))),0)</f>
-        <v>10</v>
+      <c r="B24" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="44"/>
+      <c r="D24" s="46">
+        <v>3.0</v>
+      </c>
+      <c r="E24" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>Simple</v>
+      </c>
+      <c r="F24" s="43">
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="36"/>
+      <c r="K24" s="39"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2692,7 +2717,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="36"/>
+      <c r="T24" s="39"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -2702,26 +2727,26 @@
     </row>
     <row r="25" ht="27.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E25" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Simple</v>
-      </c>
-      <c r="F25" s="24">
-        <f t="shared" si="6"/>
-        <v>5</v>
+      <c r="B25" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="46">
+        <v>4.0</v>
+      </c>
+      <c r="E25" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>Intermedio</v>
+      </c>
+      <c r="F25" s="43">
+        <f t="shared" si="4"/>
+        <v>10</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="36"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -2730,7 +2755,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="36"/>
+      <c r="T25" s="39"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -2740,26 +2765,26 @@
     </row>
     <row r="26" ht="27.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38">
+      <c r="B26" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="44"/>
+      <c r="D26" s="46">
         <v>3.0</v>
       </c>
-      <c r="E26" s="24" t="str">
-        <f t="shared" si="5"/>
+      <c r="E26" s="43" t="str">
+        <f t="shared" si="3"/>
         <v>Simple</v>
       </c>
-      <c r="F26" s="24">
-        <f t="shared" si="6"/>
+      <c r="F26" s="43">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="36"/>
+      <c r="K26" s="39"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -2768,7 +2793,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="36"/>
+      <c r="T26" s="39"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -2778,26 +2803,16 @@
     </row>
     <row r="27" ht="27.75" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="21" t="s">
-        <v>40</v>
-      </c>
+      <c r="B27" s="21"/>
       <c r="C27" s="21"/>
-      <c r="D27" s="38">
-        <v>4.0</v>
-      </c>
-      <c r="E27" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Intermedio</v>
-      </c>
-      <c r="F27" s="24">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
+      <c r="D27" s="48"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="36"/>
+      <c r="K27" s="39"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -2806,7 +2821,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="36"/>
+      <c r="T27" s="39"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -2816,26 +2831,16 @@
     </row>
     <row r="28" ht="27.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E28" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Simple</v>
-      </c>
-      <c r="F28" s="24">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="36"/>
+      <c r="K28" s="39"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -2844,7 +2849,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="36"/>
+      <c r="T28" s="39"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -2854,21 +2859,21 @@
     </row>
     <row r="29" ht="27.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="43">
+      <c r="B29" s="50"/>
+      <c r="C29" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54">
         <f>SUM(F16:F28)</f>
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="36"/>
+      <c r="K29" s="39"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -2877,7 +2882,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="36"/>
+      <c r="T29" s="39"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -2896,7 +2901,7 @@
       <c r="H30" s="18"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="36"/>
+      <c r="K30" s="39"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -2943,17 +2948,17 @@
     </row>
     <row r="32" ht="27.75" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="44"/>
+        <v>39</v>
+      </c>
+      <c r="B32" s="55"/>
       <c r="C32" s="29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="7"/>
       <c r="F32" s="30">
         <f>G12+F29</f>
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -3034,25 +3039,25 @@
     </row>
     <row r="35" ht="27.75" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -3076,27 +3081,27 @@
     </row>
     <row r="36" ht="27.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="47">
+      <c r="B36" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="58">
         <v>2.0</v>
       </c>
       <c r="F36" s="25">
         <v>0.0</v>
       </c>
-      <c r="G36" s="48">
-        <f t="shared" ref="G36:G48" si="7">E36*F36</f>
+      <c r="G36" s="59">
+        <f t="shared" ref="G36:G48" si="5">E36*F36</f>
         <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I36" s="18"/>
       <c r="J36" s="18"/>
@@ -3119,27 +3124,27 @@
     </row>
     <row r="37" ht="27.75" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="45" t="s">
+      <c r="B37" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="48">
+      <c r="E37" s="59">
         <v>2.0</v>
       </c>
       <c r="F37" s="25">
         <v>5.0</v>
       </c>
-      <c r="G37" s="48">
-        <f t="shared" si="7"/>
+      <c r="G37" s="59">
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="H37" s="50" t="s">
-        <v>57</v>
+      <c r="H37" s="61" t="s">
+        <v>53</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -3162,21 +3167,21 @@
     </row>
     <row r="38" ht="27.0" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="48">
+      <c r="B38" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="60"/>
+      <c r="E38" s="59">
         <v>1.0</v>
       </c>
       <c r="F38" s="25">
         <v>5.0</v>
       </c>
-      <c r="G38" s="48">
-        <f t="shared" si="7"/>
+      <c r="G38" s="59">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H38" s="1"/>
@@ -3201,23 +3206,23 @@
     </row>
     <row r="39" ht="27.75" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="48">
+      <c r="B39" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="59">
         <v>1.0</v>
       </c>
       <c r="F39" s="25">
         <v>3.0</v>
       </c>
-      <c r="G39" s="48">
-        <f t="shared" si="7"/>
+      <c r="G39" s="59">
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="H39" s="1"/>
@@ -3242,23 +3247,23 @@
     </row>
     <row r="40" ht="30.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="47">
+      <c r="B40" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="58">
         <v>1.0</v>
       </c>
       <c r="F40" s="25">
         <v>0.0</v>
       </c>
-      <c r="G40" s="48">
-        <f t="shared" si="7"/>
+      <c r="G40" s="59">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H40" s="1"/>
@@ -3283,23 +3288,23 @@
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="E41" s="47">
+      <c r="B41" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="58">
         <v>0.5</v>
       </c>
       <c r="F41" s="25">
         <v>3.0</v>
       </c>
-      <c r="G41" s="48">
-        <f t="shared" si="7"/>
+      <c r="G41" s="59">
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="H41" s="1"/>
@@ -3324,23 +3329,23 @@
     </row>
     <row r="42" ht="27.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="47">
+      <c r="B42" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="58">
         <v>0.5</v>
       </c>
       <c r="F42" s="25">
         <v>5.0</v>
       </c>
-      <c r="G42" s="48">
-        <f t="shared" si="7"/>
+      <c r="G42" s="59">
+        <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
       <c r="H42" s="1"/>
@@ -3365,23 +3370,23 @@
     </row>
     <row r="43" ht="27.75" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="47">
+      <c r="B43" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="58">
         <v>2.0</v>
       </c>
       <c r="F43" s="25">
         <v>3.0</v>
       </c>
-      <c r="G43" s="48">
-        <f t="shared" si="7"/>
+      <c r="G43" s="59">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="H43" s="1"/>
@@ -3406,23 +3411,23 @@
     </row>
     <row r="44" ht="27.75" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="47">
+      <c r="B44" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="58">
         <v>1.0</v>
       </c>
       <c r="F44" s="25">
         <v>0.0</v>
       </c>
-      <c r="G44" s="48">
-        <f t="shared" si="7"/>
+      <c r="G44" s="59">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H44" s="1"/>
@@ -3447,21 +3452,21 @@
     </row>
     <row r="45" ht="27.75" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="46"/>
-      <c r="E45" s="47">
+      <c r="B45" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="57"/>
+      <c r="E45" s="58">
         <v>1.0</v>
       </c>
       <c r="F45" s="25">
         <v>5.0</v>
       </c>
-      <c r="G45" s="48">
-        <f t="shared" si="7"/>
+      <c r="G45" s="59">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H45" s="1"/>
@@ -3486,23 +3491,23 @@
     </row>
     <row r="46" ht="27.75" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="48">
+      <c r="B46" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="59">
         <v>1.0</v>
       </c>
       <c r="F46" s="25">
         <v>5.0</v>
       </c>
-      <c r="G46" s="48">
-        <f t="shared" si="7"/>
+      <c r="G46" s="59">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H46" s="1"/>
@@ -3527,23 +3532,23 @@
     </row>
     <row r="47" ht="30.75" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="48">
+      <c r="B47" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="59">
         <v>1.0</v>
       </c>
       <c r="F47" s="25">
         <v>5.0</v>
       </c>
-      <c r="G47" s="48">
-        <f t="shared" si="7"/>
+      <c r="G47" s="59">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H47" s="1"/>
@@ -3568,23 +3573,23 @@
     </row>
     <row r="48" ht="31.5" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="47">
+      <c r="B48" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="58">
         <v>1.0</v>
       </c>
       <c r="F48" s="25">
         <v>4.0</v>
       </c>
-      <c r="G48" s="48">
-        <f t="shared" si="7"/>
+      <c r="G48" s="59">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="H48" s="1"/>
@@ -3610,13 +3615,13 @@
     <row r="49" ht="30.75" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="7"/>
-      <c r="G49" s="51">
+      <c r="G49" s="62">
         <f>SUM(G36:G48)</f>
         <v>47</v>
       </c>
@@ -3643,13 +3648,13 @@
     <row r="50" ht="27.75" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
-      <c r="G50" s="43">
+      <c r="G50" s="54">
         <f>0.6+(0.01*G49)</f>
         <v>1.07</v>
       </c>
@@ -3703,12 +3708,12 @@
     </row>
     <row r="52" ht="27.75" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -3731,25 +3736,25 @@
     </row>
     <row r="53" ht="27.75" customHeight="1">
       <c r="A53" s="18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -3773,27 +3778,27 @@
     </row>
     <row r="54" ht="64.5" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D54" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="47">
+      <c r="B54" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="58">
         <v>1.5</v>
       </c>
       <c r="F54" s="25">
         <v>3.0</v>
       </c>
-      <c r="G54" s="48">
-        <f t="shared" ref="G54:G61" si="8">E54*F54</f>
+      <c r="G54" s="59">
+        <f t="shared" ref="G54:G61" si="6">E54*F54</f>
         <v>4.5</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I54" s="18"/>
       <c r="J54" s="18"/>
@@ -3816,27 +3821,27 @@
     </row>
     <row r="55" ht="51.0" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="45" t="s">
+      <c r="B55" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="D55" s="49" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" s="47">
+      <c r="E55" s="58">
         <v>0.5</v>
       </c>
-      <c r="F55" s="55">
+      <c r="F55" s="66">
         <v>4.0</v>
       </c>
-      <c r="G55" s="48">
-        <f t="shared" si="8"/>
+      <c r="G55" s="59">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H55" s="50" t="s">
-        <v>57</v>
+      <c r="H55" s="61" t="s">
+        <v>53</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -3859,23 +3864,23 @@
     </row>
     <row r="56" ht="48.75" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D56" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="E56" s="47">
+      <c r="B56" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="E56" s="58">
         <v>1.0</v>
       </c>
       <c r="F56" s="25">
         <v>4.0</v>
       </c>
-      <c r="G56" s="48">
-        <f t="shared" si="8"/>
+      <c r="G56" s="59">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H56" s="1"/>
@@ -3900,23 +3905,23 @@
     </row>
     <row r="57" ht="46.5" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="E57" s="47">
+      <c r="B57" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="58">
         <v>0.5</v>
       </c>
       <c r="F57" s="25">
         <v>3.0</v>
       </c>
-      <c r="G57" s="48">
-        <f t="shared" si="8"/>
+      <c r="G57" s="59">
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="H57" s="1"/>
@@ -3941,23 +3946,23 @@
     </row>
     <row r="58" ht="37.5" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D58" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E58" s="47">
+      <c r="B58" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="58">
         <v>1.0</v>
       </c>
       <c r="F58" s="25">
         <v>4.0</v>
       </c>
-      <c r="G58" s="48">
-        <f t="shared" si="8"/>
+      <c r="G58" s="59">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H58" s="1"/>
@@ -3982,23 +3987,23 @@
     </row>
     <row r="59" ht="43.5" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="E59" s="47">
+      <c r="B59" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" s="58">
         <v>2.0</v>
       </c>
       <c r="F59" s="25">
         <v>2.0</v>
       </c>
-      <c r="G59" s="48">
-        <f t="shared" si="8"/>
+      <c r="G59" s="59">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H59" s="1"/>
@@ -4023,23 +4028,23 @@
     </row>
     <row r="60" ht="71.25" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="C60" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D60" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="E60" s="47">
+      <c r="B60" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="58">
         <v>-1.0</v>
       </c>
       <c r="F60" s="25">
         <v>4.0</v>
       </c>
-      <c r="G60" s="48">
-        <f t="shared" si="8"/>
+      <c r="G60" s="59">
+        <f t="shared" si="6"/>
         <v>-4</v>
       </c>
       <c r="H60" s="1"/>
@@ -4064,23 +4069,23 @@
     </row>
     <row r="61" ht="62.25" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="C61" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="D61" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="E61" s="47">
+      <c r="B61" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="58">
         <v>-1.0</v>
       </c>
-      <c r="F61" s="55">
+      <c r="F61" s="66">
         <v>4.0</v>
       </c>
-      <c r="G61" s="48">
-        <f t="shared" si="8"/>
+      <c r="G61" s="59">
+        <f t="shared" si="6"/>
         <v>-4</v>
       </c>
       <c r="H61" s="1"/>
@@ -4106,7 +4111,7 @@
     <row r="62" ht="38.25" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="29" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -4139,7 +4144,7 @@
     <row r="63" ht="27.75" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="29" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -4172,11 +4177,11 @@
     <row r="64" ht="27.75" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="29"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="59" t="s">
-        <v>108</v>
+      <c r="C64" s="68"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="70" t="s">
+        <v>104</v>
       </c>
       <c r="G64" s="19">
         <f>COUNTIF($F$54:$F$59,"&lt;3")+COUNTIF($F$60:$F$61,"&gt;3")</f>
@@ -4260,18 +4265,18 @@
     </row>
     <row r="67" ht="27.75" customHeight="1">
       <c r="A67" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B67" s="60" t="s">
-        <v>110</v>
+        <v>105</v>
+      </c>
+      <c r="B67" s="71" t="s">
+        <v>106</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="7"/>
-      <c r="G67" s="61">
+      <c r="G67" s="72">
         <f>F32*G50*G63</f>
-        <v>115.7312</v>
+        <v>109.0544</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -4350,22 +4355,22 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" ht="27.75" customHeight="1">
-      <c r="A70" s="62" t="s">
-        <v>111</v>
+      <c r="A70" s="73" t="s">
+        <v>107</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="1"/>
       <c r="G70" s="20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -4389,20 +4394,20 @@
     </row>
     <row r="71" ht="31.5" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="63">
+      <c r="B71" s="74">
         <v>20.0</v>
       </c>
-      <c r="C71" s="63">
+      <c r="C71" s="74">
         <f>IF($G$64&gt;=5,36,IF(AND(G$64&gt;2,$G$64&lt;=4),28, IF(AND($G$64&gt;=0,$G$64&lt;=2),20,"error")))</f>
         <v>28</v>
       </c>
-      <c r="D71" s="64">
+      <c r="D71" s="75">
         <f>IF($G$64&gt;=5,$G$71*(36/20),IF(AND($G$64&gt;2,$G$64&lt;=4),$G$71*(28/20), IF(AND($G$64&gt;=0,$G$64&lt;=2),$G$71,"error")))</f>
         <v>2.8</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="65">
+      <c r="G71" s="76">
         <v>2.0</v>
       </c>
       <c r="H71" s="1"/>
@@ -4427,8 +4432,8 @@
     </row>
     <row r="72" ht="27.75" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="66" t="s">
-        <v>116</v>
+      <c r="B72" s="77" t="s">
+        <v>112</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="7"/>
@@ -4456,20 +4461,20 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" ht="27.75" customHeight="1">
-      <c r="A73" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B73" s="63">
-        <f t="shared" ref="B73:D73" si="9">$G$67*B71</f>
-        <v>2314.624</v>
-      </c>
-      <c r="C73" s="63">
-        <f t="shared" si="9"/>
-        <v>3240.4736</v>
-      </c>
-      <c r="D73" s="63">
-        <f t="shared" si="9"/>
-        <v>324.04736</v>
+      <c r="A73" s="78" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73" s="74">
+        <f t="shared" ref="B73:D73" si="7">$G$67*B71</f>
+        <v>2181.088</v>
+      </c>
+      <c r="C73" s="74">
+        <f t="shared" si="7"/>
+        <v>3053.5232</v>
+      </c>
+      <c r="D73" s="74">
+        <f t="shared" si="7"/>
+        <v>305.35232</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="1"/>
@@ -4495,20 +4500,20 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" ht="27.75" customHeight="1">
-      <c r="A74" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="B74" s="68">
-        <f t="shared" ref="B74:C74" si="10">B73/(22*8)</f>
-        <v>13.15127273</v>
-      </c>
-      <c r="C74" s="68">
-        <f t="shared" si="10"/>
-        <v>18.41178182</v>
-      </c>
-      <c r="D74" s="69">
+      <c r="A74" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="B74" s="79">
+        <f t="shared" ref="B74:C74" si="8">B73/(22*8)</f>
+        <v>12.39254545</v>
+      </c>
+      <c r="C74" s="79">
+        <f t="shared" si="8"/>
+        <v>17.34956364</v>
+      </c>
+      <c r="D74" s="80">
         <f>D73/(22*3)</f>
-        <v>4.909808485</v>
+        <v>4.626550303</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="1"/>
@@ -4591,15 +4596,15 @@
     </row>
     <row r="77" ht="27.75" customHeight="1">
       <c r="A77" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B77" s="70" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="71"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="72"/>
+        <v>115</v>
+      </c>
+      <c r="B77" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" s="82"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="68"/>
+      <c r="F77" s="83"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -4623,20 +4628,20 @@
     </row>
     <row r="78" ht="27.75" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="44" t="s">
+      <c r="B78" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D78" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="E78" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="F78" s="72" t="s">
         <v>121</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D78" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="E78" s="61" t="s">
-        <v>124</v>
-      </c>
-      <c r="F78" s="61" t="s">
-        <v>125</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -4661,23 +4666,23 @@
     </row>
     <row r="79" ht="27.75" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="C79" s="74">
+      <c r="B79" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="C79" s="85">
         <v>0.4</v>
       </c>
-      <c r="D79" s="68">
-        <f t="shared" ref="D79:F79" si="11">$C79/$C$79*B$74</f>
-        <v>13.15127273</v>
-      </c>
-      <c r="E79" s="68">
-        <f t="shared" si="11"/>
-        <v>18.41178182</v>
-      </c>
-      <c r="F79" s="68">
-        <f t="shared" si="11"/>
-        <v>4.909808485</v>
+      <c r="D79" s="79">
+        <f t="shared" ref="D79:F79" si="9">$C79/$C$79*B$74</f>
+        <v>12.39254545</v>
+      </c>
+      <c r="E79" s="79">
+        <f t="shared" si="9"/>
+        <v>17.34956364</v>
+      </c>
+      <c r="F79" s="79">
+        <f t="shared" si="9"/>
+        <v>4.626550303</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -4702,24 +4707,24 @@
     </row>
     <row r="80" ht="27.75" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="C80" s="74">
+      <c r="B80" s="84" t="s">
+        <v>123</v>
+      </c>
+      <c r="C80" s="85">
         <f>1-C79</f>
         <v>0.6</v>
       </c>
-      <c r="D80" s="63">
-        <f t="shared" ref="D80:F80" si="12">$C80/$C$79*B$74</f>
-        <v>19.72690909</v>
-      </c>
-      <c r="E80" s="63">
-        <f t="shared" si="12"/>
-        <v>27.61767273</v>
-      </c>
-      <c r="F80" s="63">
-        <f t="shared" si="12"/>
-        <v>7.364712727</v>
+      <c r="D80" s="74">
+        <f t="shared" ref="D80:F80" si="10">$C80/$C$79*B$74</f>
+        <v>18.58881818</v>
+      </c>
+      <c r="E80" s="74">
+        <f t="shared" si="10"/>
+        <v>26.02434545</v>
+      </c>
+      <c r="F80" s="74">
+        <f t="shared" si="10"/>
+        <v>6.939825455</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -4744,22 +4749,22 @@
     </row>
     <row r="81" ht="27.75" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="75"/>
-      <c r="C81" s="74">
+      <c r="B81" s="86"/>
+      <c r="C81" s="85">
         <f>SUM(C79:C80)</f>
         <v>1</v>
       </c>
-      <c r="D81" s="68">
-        <f t="shared" ref="D81:F81" si="13">$C81/$C$79*B$74</f>
-        <v>32.87818182</v>
-      </c>
-      <c r="E81" s="68">
-        <f t="shared" si="13"/>
-        <v>46.02945455</v>
-      </c>
-      <c r="F81" s="68">
-        <f t="shared" si="13"/>
-        <v>12.27452121</v>
+      <c r="D81" s="79">
+        <f t="shared" ref="D81:F81" si="11">$C81/$C$79*B$74</f>
+        <v>30.98136364</v>
+      </c>
+      <c r="E81" s="79">
+        <f t="shared" si="11"/>
+        <v>43.37390909</v>
+      </c>
+      <c r="F81" s="79">
+        <f t="shared" si="11"/>
+        <v>11.56637576</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -4812,7 +4817,7 @@
     </row>
     <row r="83" ht="27.75" customHeight="1">
       <c r="A83" s="18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B83" s="25">
         <v>5.0</v>
@@ -4872,16 +4877,16 @@
     </row>
     <row r="85" ht="27.75" customHeight="1">
       <c r="A85" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="B85" s="61" t="s">
-        <v>130</v>
-      </c>
-      <c r="C85" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="D85" s="61" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="B85" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="D85" s="72" t="s">
+        <v>128</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="1"/>
@@ -4907,22 +4912,22 @@
       <c r="Z85" s="1"/>
     </row>
     <row r="86" ht="27.75" customHeight="1">
-      <c r="A86" s="76"/>
-      <c r="B86" s="77">
+      <c r="A86" s="87"/>
+      <c r="B86" s="88">
         <f>$D$81/$B$83</f>
-        <v>6.575636364</v>
-      </c>
-      <c r="C86" s="77">
+        <v>6.196272727</v>
+      </c>
+      <c r="C86" s="88">
         <f>$E$81/$B$83</f>
-        <v>9.205890909</v>
-      </c>
-      <c r="D86" s="77">
+        <v>8.674781818</v>
+      </c>
+      <c r="D86" s="88">
         <f>$F$81/$B$83</f>
-        <v>2.454904242</v>
-      </c>
-      <c r="E86" s="76"/>
-      <c r="F86" s="76"/>
-      <c r="G86" s="76"/>
+        <v>2.313275152</v>
+      </c>
+      <c r="E86" s="87"/>
+      <c r="F86" s="87"/>
+      <c r="G86" s="87"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -4944,452 +4949,452 @@
       <c r="Z86" s="1"/>
     </row>
     <row r="87" ht="27.75" customHeight="1">
-      <c r="A87" s="76"/>
-      <c r="B87" s="76"/>
-      <c r="C87" s="76"/>
-      <c r="D87" s="76"/>
-      <c r="E87" s="78"/>
-      <c r="F87" s="76"/>
-      <c r="G87" s="76"/>
-      <c r="H87" s="76"/>
-      <c r="I87" s="76"/>
-      <c r="J87" s="76"/>
-      <c r="K87" s="76"/>
-      <c r="L87" s="76"/>
-      <c r="M87" s="76"/>
-      <c r="N87" s="76"/>
-      <c r="O87" s="76"/>
-      <c r="P87" s="76"/>
-      <c r="Q87" s="76"/>
-      <c r="R87" s="76"/>
-      <c r="S87" s="76"/>
-      <c r="T87" s="76"/>
-      <c r="U87" s="76"/>
-      <c r="V87" s="76"/>
-      <c r="W87" s="76"/>
-      <c r="X87" s="76"/>
-      <c r="Y87" s="76"/>
-      <c r="Z87" s="76"/>
+      <c r="A87" s="87"/>
+      <c r="B87" s="87"/>
+      <c r="C87" s="87"/>
+      <c r="D87" s="87"/>
+      <c r="E87" s="89"/>
+      <c r="F87" s="87"/>
+      <c r="G87" s="87"/>
+      <c r="H87" s="87"/>
+      <c r="I87" s="87"/>
+      <c r="J87" s="87"/>
+      <c r="K87" s="87"/>
+      <c r="L87" s="87"/>
+      <c r="M87" s="87"/>
+      <c r="N87" s="87"/>
+      <c r="O87" s="87"/>
+      <c r="P87" s="87"/>
+      <c r="Q87" s="87"/>
+      <c r="R87" s="87"/>
+      <c r="S87" s="87"/>
+      <c r="T87" s="87"/>
+      <c r="U87" s="87"/>
+      <c r="V87" s="87"/>
+      <c r="W87" s="87"/>
+      <c r="X87" s="87"/>
+      <c r="Y87" s="87"/>
+      <c r="Z87" s="87"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="76"/>
-      <c r="B88" s="76"/>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="78"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="76"/>
-      <c r="H88" s="76"/>
-      <c r="I88" s="76"/>
-      <c r="J88" s="76"/>
-      <c r="K88" s="76"/>
-      <c r="L88" s="76"/>
-      <c r="M88" s="76"/>
-      <c r="N88" s="76"/>
-      <c r="O88" s="76"/>
-      <c r="P88" s="76"/>
-      <c r="Q88" s="76"/>
-      <c r="R88" s="76"/>
-      <c r="S88" s="76"/>
-      <c r="T88" s="76"/>
-      <c r="U88" s="76"/>
-      <c r="V88" s="76"/>
-      <c r="W88" s="76"/>
-      <c r="X88" s="76"/>
-      <c r="Y88" s="76"/>
-      <c r="Z88" s="76"/>
+      <c r="A88" s="87"/>
+      <c r="B88" s="87"/>
+      <c r="C88" s="87"/>
+      <c r="D88" s="87"/>
+      <c r="E88" s="89"/>
+      <c r="F88" s="87"/>
+      <c r="G88" s="87"/>
+      <c r="H88" s="87"/>
+      <c r="I88" s="87"/>
+      <c r="J88" s="87"/>
+      <c r="K88" s="87"/>
+      <c r="L88" s="87"/>
+      <c r="M88" s="87"/>
+      <c r="N88" s="87"/>
+      <c r="O88" s="87"/>
+      <c r="P88" s="87"/>
+      <c r="Q88" s="87"/>
+      <c r="R88" s="87"/>
+      <c r="S88" s="87"/>
+      <c r="T88" s="87"/>
+      <c r="U88" s="87"/>
+      <c r="V88" s="87"/>
+      <c r="W88" s="87"/>
+      <c r="X88" s="87"/>
+      <c r="Y88" s="87"/>
+      <c r="Z88" s="87"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="76"/>
-      <c r="B89" s="76"/>
-      <c r="C89" s="76"/>
-      <c r="D89" s="76"/>
-      <c r="E89" s="78"/>
-      <c r="F89" s="76"/>
-      <c r="G89" s="76"/>
-      <c r="H89" s="76"/>
-      <c r="I89" s="76"/>
-      <c r="J89" s="76"/>
-      <c r="K89" s="76"/>
-      <c r="L89" s="76"/>
-      <c r="M89" s="76"/>
-      <c r="N89" s="76"/>
-      <c r="O89" s="76"/>
-      <c r="P89" s="76"/>
-      <c r="Q89" s="76"/>
-      <c r="R89" s="76"/>
-      <c r="S89" s="76"/>
-      <c r="T89" s="76"/>
-      <c r="U89" s="76"/>
-      <c r="V89" s="76"/>
-      <c r="W89" s="76"/>
-      <c r="X89" s="76"/>
-      <c r="Y89" s="76"/>
-      <c r="Z89" s="76"/>
+      <c r="A89" s="87"/>
+      <c r="B89" s="87"/>
+      <c r="C89" s="87"/>
+      <c r="D89" s="87"/>
+      <c r="E89" s="89"/>
+      <c r="F89" s="87"/>
+      <c r="G89" s="87"/>
+      <c r="H89" s="87"/>
+      <c r="I89" s="87"/>
+      <c r="J89" s="87"/>
+      <c r="K89" s="87"/>
+      <c r="L89" s="87"/>
+      <c r="M89" s="87"/>
+      <c r="N89" s="87"/>
+      <c r="O89" s="87"/>
+      <c r="P89" s="87"/>
+      <c r="Q89" s="87"/>
+      <c r="R89" s="87"/>
+      <c r="S89" s="87"/>
+      <c r="T89" s="87"/>
+      <c r="U89" s="87"/>
+      <c r="V89" s="87"/>
+      <c r="W89" s="87"/>
+      <c r="X89" s="87"/>
+      <c r="Y89" s="87"/>
+      <c r="Z89" s="87"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="76"/>
-      <c r="B90" s="76"/>
-      <c r="C90" s="76"/>
-      <c r="D90" s="76"/>
-      <c r="E90" s="78"/>
-      <c r="F90" s="76"/>
-      <c r="G90" s="76"/>
-      <c r="H90" s="76"/>
-      <c r="I90" s="76"/>
-      <c r="J90" s="76"/>
-      <c r="K90" s="76"/>
-      <c r="L90" s="76"/>
-      <c r="M90" s="76"/>
-      <c r="N90" s="76"/>
-      <c r="O90" s="76"/>
-      <c r="P90" s="76"/>
-      <c r="Q90" s="76"/>
-      <c r="R90" s="76"/>
-      <c r="S90" s="76"/>
-      <c r="T90" s="76"/>
-      <c r="U90" s="76"/>
-      <c r="V90" s="76"/>
-      <c r="W90" s="76"/>
-      <c r="X90" s="76"/>
-      <c r="Y90" s="76"/>
-      <c r="Z90" s="76"/>
+      <c r="A90" s="87"/>
+      <c r="B90" s="87"/>
+      <c r="C90" s="87"/>
+      <c r="D90" s="87"/>
+      <c r="E90" s="89"/>
+      <c r="F90" s="87"/>
+      <c r="G90" s="87"/>
+      <c r="H90" s="87"/>
+      <c r="I90" s="87"/>
+      <c r="J90" s="87"/>
+      <c r="K90" s="87"/>
+      <c r="L90" s="87"/>
+      <c r="M90" s="87"/>
+      <c r="N90" s="87"/>
+      <c r="O90" s="87"/>
+      <c r="P90" s="87"/>
+      <c r="Q90" s="87"/>
+      <c r="R90" s="87"/>
+      <c r="S90" s="87"/>
+      <c r="T90" s="87"/>
+      <c r="U90" s="87"/>
+      <c r="V90" s="87"/>
+      <c r="W90" s="87"/>
+      <c r="X90" s="87"/>
+      <c r="Y90" s="87"/>
+      <c r="Z90" s="87"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="76"/>
-      <c r="B91" s="76"/>
-      <c r="C91" s="76"/>
-      <c r="D91" s="76"/>
-      <c r="E91" s="78"/>
-      <c r="F91" s="76"/>
-      <c r="G91" s="76"/>
-      <c r="H91" s="76"/>
-      <c r="I91" s="76"/>
-      <c r="J91" s="76"/>
-      <c r="K91" s="76"/>
-      <c r="L91" s="76"/>
-      <c r="M91" s="76"/>
-      <c r="N91" s="76"/>
-      <c r="O91" s="76"/>
-      <c r="P91" s="76"/>
-      <c r="Q91" s="76"/>
-      <c r="R91" s="76"/>
-      <c r="S91" s="76"/>
-      <c r="T91" s="76"/>
-      <c r="U91" s="76"/>
-      <c r="V91" s="76"/>
-      <c r="W91" s="76"/>
-      <c r="X91" s="76"/>
-      <c r="Y91" s="76"/>
-      <c r="Z91" s="76"/>
+      <c r="A91" s="87"/>
+      <c r="B91" s="87"/>
+      <c r="C91" s="87"/>
+      <c r="D91" s="87"/>
+      <c r="E91" s="89"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="87"/>
+      <c r="I91" s="87"/>
+      <c r="J91" s="87"/>
+      <c r="K91" s="87"/>
+      <c r="L91" s="87"/>
+      <c r="M91" s="87"/>
+      <c r="N91" s="87"/>
+      <c r="O91" s="87"/>
+      <c r="P91" s="87"/>
+      <c r="Q91" s="87"/>
+      <c r="R91" s="87"/>
+      <c r="S91" s="87"/>
+      <c r="T91" s="87"/>
+      <c r="U91" s="87"/>
+      <c r="V91" s="87"/>
+      <c r="W91" s="87"/>
+      <c r="X91" s="87"/>
+      <c r="Y91" s="87"/>
+      <c r="Z91" s="87"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="76"/>
-      <c r="B92" s="76"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
-      <c r="E92" s="78"/>
-      <c r="F92" s="76"/>
-      <c r="G92" s="76"/>
-      <c r="H92" s="76"/>
-      <c r="I92" s="76"/>
-      <c r="J92" s="76"/>
-      <c r="K92" s="76"/>
-      <c r="L92" s="76"/>
-      <c r="M92" s="76"/>
-      <c r="N92" s="76"/>
-      <c r="O92" s="76"/>
-      <c r="P92" s="76"/>
-      <c r="Q92" s="76"/>
-      <c r="R92" s="76"/>
-      <c r="S92" s="76"/>
-      <c r="T92" s="76"/>
-      <c r="U92" s="76"/>
-      <c r="V92" s="76"/>
-      <c r="W92" s="76"/>
-      <c r="X92" s="76"/>
-      <c r="Y92" s="76"/>
-      <c r="Z92" s="76"/>
+      <c r="A92" s="87"/>
+      <c r="B92" s="87"/>
+      <c r="C92" s="87"/>
+      <c r="D92" s="87"/>
+      <c r="E92" s="89"/>
+      <c r="F92" s="87"/>
+      <c r="G92" s="87"/>
+      <c r="H92" s="87"/>
+      <c r="I92" s="87"/>
+      <c r="J92" s="87"/>
+      <c r="K92" s="87"/>
+      <c r="L92" s="87"/>
+      <c r="M92" s="87"/>
+      <c r="N92" s="87"/>
+      <c r="O92" s="87"/>
+      <c r="P92" s="87"/>
+      <c r="Q92" s="87"/>
+      <c r="R92" s="87"/>
+      <c r="S92" s="87"/>
+      <c r="T92" s="87"/>
+      <c r="U92" s="87"/>
+      <c r="V92" s="87"/>
+      <c r="W92" s="87"/>
+      <c r="X92" s="87"/>
+      <c r="Y92" s="87"/>
+      <c r="Z92" s="87"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="76"/>
-      <c r="B93" s="76"/>
-      <c r="C93" s="76"/>
-      <c r="D93" s="76"/>
-      <c r="E93" s="78"/>
-      <c r="F93" s="76"/>
-      <c r="G93" s="76"/>
-      <c r="H93" s="76"/>
-      <c r="I93" s="76"/>
-      <c r="J93" s="76"/>
-      <c r="K93" s="76"/>
-      <c r="L93" s="76"/>
-      <c r="M93" s="76"/>
-      <c r="N93" s="76"/>
-      <c r="O93" s="76"/>
-      <c r="P93" s="76"/>
-      <c r="Q93" s="76"/>
-      <c r="R93" s="76"/>
-      <c r="S93" s="76"/>
-      <c r="T93" s="76"/>
-      <c r="U93" s="76"/>
-      <c r="V93" s="76"/>
-      <c r="W93" s="76"/>
-      <c r="X93" s="76"/>
-      <c r="Y93" s="76"/>
-      <c r="Z93" s="76"/>
+      <c r="A93" s="87"/>
+      <c r="B93" s="87"/>
+      <c r="C93" s="87"/>
+      <c r="D93" s="87"/>
+      <c r="E93" s="89"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="87"/>
+      <c r="I93" s="87"/>
+      <c r="J93" s="87"/>
+      <c r="K93" s="87"/>
+      <c r="L93" s="87"/>
+      <c r="M93" s="87"/>
+      <c r="N93" s="87"/>
+      <c r="O93" s="87"/>
+      <c r="P93" s="87"/>
+      <c r="Q93" s="87"/>
+      <c r="R93" s="87"/>
+      <c r="S93" s="87"/>
+      <c r="T93" s="87"/>
+      <c r="U93" s="87"/>
+      <c r="V93" s="87"/>
+      <c r="W93" s="87"/>
+      <c r="X93" s="87"/>
+      <c r="Y93" s="87"/>
+      <c r="Z93" s="87"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="76"/>
-      <c r="B94" s="76"/>
-      <c r="C94" s="76"/>
-      <c r="D94" s="76"/>
-      <c r="E94" s="78"/>
-      <c r="F94" s="76"/>
-      <c r="G94" s="76"/>
-      <c r="H94" s="76"/>
-      <c r="I94" s="76"/>
-      <c r="J94" s="76"/>
-      <c r="K94" s="76"/>
-      <c r="L94" s="76"/>
-      <c r="M94" s="76"/>
-      <c r="N94" s="76"/>
-      <c r="O94" s="76"/>
-      <c r="P94" s="76"/>
-      <c r="Q94" s="76"/>
-      <c r="R94" s="76"/>
-      <c r="S94" s="76"/>
-      <c r="T94" s="76"/>
-      <c r="U94" s="76"/>
-      <c r="V94" s="76"/>
-      <c r="W94" s="76"/>
-      <c r="X94" s="76"/>
-      <c r="Y94" s="76"/>
-      <c r="Z94" s="76"/>
+      <c r="A94" s="87"/>
+      <c r="B94" s="87"/>
+      <c r="C94" s="87"/>
+      <c r="D94" s="87"/>
+      <c r="E94" s="89"/>
+      <c r="F94" s="87"/>
+      <c r="G94" s="87"/>
+      <c r="H94" s="87"/>
+      <c r="I94" s="87"/>
+      <c r="J94" s="87"/>
+      <c r="K94" s="87"/>
+      <c r="L94" s="87"/>
+      <c r="M94" s="87"/>
+      <c r="N94" s="87"/>
+      <c r="O94" s="87"/>
+      <c r="P94" s="87"/>
+      <c r="Q94" s="87"/>
+      <c r="R94" s="87"/>
+      <c r="S94" s="87"/>
+      <c r="T94" s="87"/>
+      <c r="U94" s="87"/>
+      <c r="V94" s="87"/>
+      <c r="W94" s="87"/>
+      <c r="X94" s="87"/>
+      <c r="Y94" s="87"/>
+      <c r="Z94" s="87"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="76"/>
-      <c r="B95" s="76"/>
-      <c r="C95" s="76"/>
-      <c r="D95" s="76"/>
-      <c r="E95" s="78"/>
-      <c r="F95" s="76"/>
-      <c r="G95" s="76"/>
-      <c r="H95" s="76"/>
-      <c r="I95" s="76"/>
-      <c r="J95" s="76"/>
-      <c r="K95" s="76"/>
-      <c r="L95" s="76"/>
-      <c r="M95" s="76"/>
-      <c r="N95" s="76"/>
-      <c r="O95" s="76"/>
-      <c r="P95" s="76"/>
-      <c r="Q95" s="76"/>
-      <c r="R95" s="76"/>
-      <c r="S95" s="76"/>
-      <c r="T95" s="76"/>
-      <c r="U95" s="76"/>
-      <c r="V95" s="76"/>
-      <c r="W95" s="76"/>
-      <c r="X95" s="76"/>
-      <c r="Y95" s="76"/>
-      <c r="Z95" s="76"/>
+      <c r="A95" s="87"/>
+      <c r="B95" s="87"/>
+      <c r="C95" s="87"/>
+      <c r="D95" s="87"/>
+      <c r="E95" s="89"/>
+      <c r="F95" s="87"/>
+      <c r="G95" s="87"/>
+      <c r="H95" s="87"/>
+      <c r="I95" s="87"/>
+      <c r="J95" s="87"/>
+      <c r="K95" s="87"/>
+      <c r="L95" s="87"/>
+      <c r="M95" s="87"/>
+      <c r="N95" s="87"/>
+      <c r="O95" s="87"/>
+      <c r="P95" s="87"/>
+      <c r="Q95" s="87"/>
+      <c r="R95" s="87"/>
+      <c r="S95" s="87"/>
+      <c r="T95" s="87"/>
+      <c r="U95" s="87"/>
+      <c r="V95" s="87"/>
+      <c r="W95" s="87"/>
+      <c r="X95" s="87"/>
+      <c r="Y95" s="87"/>
+      <c r="Z95" s="87"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="76"/>
-      <c r="B96" s="76"/>
-      <c r="C96" s="76"/>
-      <c r="D96" s="76"/>
-      <c r="E96" s="78"/>
-      <c r="F96" s="76"/>
-      <c r="G96" s="76"/>
-      <c r="H96" s="76"/>
-      <c r="I96" s="76"/>
-      <c r="J96" s="76"/>
-      <c r="K96" s="76"/>
-      <c r="L96" s="76"/>
-      <c r="M96" s="76"/>
-      <c r="N96" s="76"/>
-      <c r="O96" s="76"/>
-      <c r="P96" s="76"/>
-      <c r="Q96" s="76"/>
-      <c r="R96" s="76"/>
-      <c r="S96" s="76"/>
-      <c r="T96" s="76"/>
-      <c r="U96" s="76"/>
-      <c r="V96" s="76"/>
-      <c r="W96" s="76"/>
-      <c r="X96" s="76"/>
-      <c r="Y96" s="76"/>
-      <c r="Z96" s="76"/>
+      <c r="A96" s="87"/>
+      <c r="B96" s="87"/>
+      <c r="C96" s="87"/>
+      <c r="D96" s="87"/>
+      <c r="E96" s="89"/>
+      <c r="F96" s="87"/>
+      <c r="G96" s="87"/>
+      <c r="H96" s="87"/>
+      <c r="I96" s="87"/>
+      <c r="J96" s="87"/>
+      <c r="K96" s="87"/>
+      <c r="L96" s="87"/>
+      <c r="M96" s="87"/>
+      <c r="N96" s="87"/>
+      <c r="O96" s="87"/>
+      <c r="P96" s="87"/>
+      <c r="Q96" s="87"/>
+      <c r="R96" s="87"/>
+      <c r="S96" s="87"/>
+      <c r="T96" s="87"/>
+      <c r="U96" s="87"/>
+      <c r="V96" s="87"/>
+      <c r="W96" s="87"/>
+      <c r="X96" s="87"/>
+      <c r="Y96" s="87"/>
+      <c r="Z96" s="87"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="76"/>
-      <c r="B97" s="76"/>
-      <c r="C97" s="76"/>
-      <c r="D97" s="76"/>
-      <c r="E97" s="78"/>
-      <c r="F97" s="76"/>
-      <c r="G97" s="76"/>
-      <c r="H97" s="76"/>
-      <c r="I97" s="76"/>
-      <c r="J97" s="76"/>
-      <c r="K97" s="76"/>
-      <c r="L97" s="76"/>
-      <c r="M97" s="76"/>
-      <c r="N97" s="76"/>
-      <c r="O97" s="76"/>
-      <c r="P97" s="76"/>
-      <c r="Q97" s="76"/>
-      <c r="R97" s="76"/>
-      <c r="S97" s="76"/>
-      <c r="T97" s="76"/>
-      <c r="U97" s="76"/>
-      <c r="V97" s="76"/>
-      <c r="W97" s="76"/>
-      <c r="X97" s="76"/>
-      <c r="Y97" s="76"/>
-      <c r="Z97" s="76"/>
+      <c r="A97" s="87"/>
+      <c r="B97" s="87"/>
+      <c r="C97" s="87"/>
+      <c r="D97" s="87"/>
+      <c r="E97" s="89"/>
+      <c r="F97" s="87"/>
+      <c r="G97" s="87"/>
+      <c r="H97" s="87"/>
+      <c r="I97" s="87"/>
+      <c r="J97" s="87"/>
+      <c r="K97" s="87"/>
+      <c r="L97" s="87"/>
+      <c r="M97" s="87"/>
+      <c r="N97" s="87"/>
+      <c r="O97" s="87"/>
+      <c r="P97" s="87"/>
+      <c r="Q97" s="87"/>
+      <c r="R97" s="87"/>
+      <c r="S97" s="87"/>
+      <c r="T97" s="87"/>
+      <c r="U97" s="87"/>
+      <c r="V97" s="87"/>
+      <c r="W97" s="87"/>
+      <c r="X97" s="87"/>
+      <c r="Y97" s="87"/>
+      <c r="Z97" s="87"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="76"/>
-      <c r="B98" s="76"/>
-      <c r="C98" s="76"/>
-      <c r="D98" s="76"/>
-      <c r="E98" s="78"/>
-      <c r="F98" s="76"/>
-      <c r="G98" s="76"/>
-      <c r="H98" s="76"/>
-      <c r="I98" s="76"/>
-      <c r="J98" s="76"/>
-      <c r="K98" s="76"/>
-      <c r="L98" s="76"/>
-      <c r="M98" s="76"/>
-      <c r="N98" s="76"/>
-      <c r="O98" s="76"/>
-      <c r="P98" s="76"/>
-      <c r="Q98" s="76"/>
-      <c r="R98" s="76"/>
-      <c r="S98" s="76"/>
-      <c r="T98" s="76"/>
-      <c r="U98" s="76"/>
-      <c r="V98" s="76"/>
-      <c r="W98" s="76"/>
-      <c r="X98" s="76"/>
-      <c r="Y98" s="76"/>
-      <c r="Z98" s="76"/>
+      <c r="A98" s="87"/>
+      <c r="B98" s="87"/>
+      <c r="C98" s="87"/>
+      <c r="D98" s="87"/>
+      <c r="E98" s="89"/>
+      <c r="F98" s="87"/>
+      <c r="G98" s="87"/>
+      <c r="H98" s="87"/>
+      <c r="I98" s="87"/>
+      <c r="J98" s="87"/>
+      <c r="K98" s="87"/>
+      <c r="L98" s="87"/>
+      <c r="M98" s="87"/>
+      <c r="N98" s="87"/>
+      <c r="O98" s="87"/>
+      <c r="P98" s="87"/>
+      <c r="Q98" s="87"/>
+      <c r="R98" s="87"/>
+      <c r="S98" s="87"/>
+      <c r="T98" s="87"/>
+      <c r="U98" s="87"/>
+      <c r="V98" s="87"/>
+      <c r="W98" s="87"/>
+      <c r="X98" s="87"/>
+      <c r="Y98" s="87"/>
+      <c r="Z98" s="87"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="76"/>
-      <c r="B99" s="76"/>
-      <c r="C99" s="76"/>
-      <c r="D99" s="76"/>
-      <c r="E99" s="78"/>
-      <c r="F99" s="76"/>
-      <c r="G99" s="76"/>
-      <c r="H99" s="76"/>
-      <c r="I99" s="76"/>
-      <c r="J99" s="76"/>
-      <c r="K99" s="76"/>
-      <c r="L99" s="76"/>
-      <c r="M99" s="76"/>
-      <c r="N99" s="76"/>
-      <c r="O99" s="76"/>
-      <c r="P99" s="76"/>
-      <c r="Q99" s="76"/>
-      <c r="R99" s="76"/>
-      <c r="S99" s="76"/>
-      <c r="T99" s="76"/>
-      <c r="U99" s="76"/>
-      <c r="V99" s="76"/>
-      <c r="W99" s="76"/>
-      <c r="X99" s="76"/>
-      <c r="Y99" s="76"/>
-      <c r="Z99" s="76"/>
+      <c r="A99" s="87"/>
+      <c r="B99" s="87"/>
+      <c r="C99" s="87"/>
+      <c r="D99" s="87"/>
+      <c r="E99" s="89"/>
+      <c r="F99" s="87"/>
+      <c r="G99" s="87"/>
+      <c r="H99" s="87"/>
+      <c r="I99" s="87"/>
+      <c r="J99" s="87"/>
+      <c r="K99" s="87"/>
+      <c r="L99" s="87"/>
+      <c r="M99" s="87"/>
+      <c r="N99" s="87"/>
+      <c r="O99" s="87"/>
+      <c r="P99" s="87"/>
+      <c r="Q99" s="87"/>
+      <c r="R99" s="87"/>
+      <c r="S99" s="87"/>
+      <c r="T99" s="87"/>
+      <c r="U99" s="87"/>
+      <c r="V99" s="87"/>
+      <c r="W99" s="87"/>
+      <c r="X99" s="87"/>
+      <c r="Y99" s="87"/>
+      <c r="Z99" s="87"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="76"/>
-      <c r="B100" s="76"/>
-      <c r="C100" s="76"/>
-      <c r="D100" s="76"/>
-      <c r="E100" s="78"/>
-      <c r="F100" s="76"/>
-      <c r="G100" s="76"/>
-      <c r="H100" s="76"/>
-      <c r="I100" s="76"/>
-      <c r="J100" s="76"/>
-      <c r="K100" s="76"/>
-      <c r="L100" s="76"/>
-      <c r="M100" s="76"/>
-      <c r="N100" s="76"/>
-      <c r="O100" s="76"/>
-      <c r="P100" s="76"/>
-      <c r="Q100" s="76"/>
-      <c r="R100" s="76"/>
-      <c r="S100" s="76"/>
-      <c r="T100" s="76"/>
-      <c r="U100" s="76"/>
-      <c r="V100" s="76"/>
-      <c r="W100" s="76"/>
-      <c r="X100" s="76"/>
-      <c r="Y100" s="76"/>
-      <c r="Z100" s="76"/>
+      <c r="A100" s="87"/>
+      <c r="B100" s="87"/>
+      <c r="C100" s="87"/>
+      <c r="D100" s="87"/>
+      <c r="E100" s="89"/>
+      <c r="F100" s="87"/>
+      <c r="G100" s="87"/>
+      <c r="H100" s="87"/>
+      <c r="I100" s="87"/>
+      <c r="J100" s="87"/>
+      <c r="K100" s="87"/>
+      <c r="L100" s="87"/>
+      <c r="M100" s="87"/>
+      <c r="N100" s="87"/>
+      <c r="O100" s="87"/>
+      <c r="P100" s="87"/>
+      <c r="Q100" s="87"/>
+      <c r="R100" s="87"/>
+      <c r="S100" s="87"/>
+      <c r="T100" s="87"/>
+      <c r="U100" s="87"/>
+      <c r="V100" s="87"/>
+      <c r="W100" s="87"/>
+      <c r="X100" s="87"/>
+      <c r="Y100" s="87"/>
+      <c r="Z100" s="87"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="76"/>
-      <c r="B101" s="76"/>
-      <c r="C101" s="76"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="76"/>
-      <c r="G101" s="76"/>
-      <c r="H101" s="76"/>
-      <c r="I101" s="76"/>
-      <c r="J101" s="76"/>
-      <c r="K101" s="76"/>
-      <c r="L101" s="76"/>
-      <c r="M101" s="76"/>
-      <c r="N101" s="76"/>
-      <c r="O101" s="76"/>
-      <c r="P101" s="76"/>
-      <c r="Q101" s="76"/>
-      <c r="R101" s="76"/>
-      <c r="S101" s="76"/>
-      <c r="T101" s="76"/>
-      <c r="U101" s="76"/>
-      <c r="V101" s="76"/>
-      <c r="W101" s="76"/>
-      <c r="X101" s="76"/>
-      <c r="Y101" s="76"/>
-      <c r="Z101" s="76"/>
+      <c r="A101" s="87"/>
+      <c r="B101" s="87"/>
+      <c r="C101" s="87"/>
+      <c r="D101" s="87"/>
+      <c r="E101" s="89"/>
+      <c r="F101" s="87"/>
+      <c r="G101" s="87"/>
+      <c r="H101" s="87"/>
+      <c r="I101" s="87"/>
+      <c r="J101" s="87"/>
+      <c r="K101" s="87"/>
+      <c r="L101" s="87"/>
+      <c r="M101" s="87"/>
+      <c r="N101" s="87"/>
+      <c r="O101" s="87"/>
+      <c r="P101" s="87"/>
+      <c r="Q101" s="87"/>
+      <c r="R101" s="87"/>
+      <c r="S101" s="87"/>
+      <c r="T101" s="87"/>
+      <c r="U101" s="87"/>
+      <c r="V101" s="87"/>
+      <c r="W101" s="87"/>
+      <c r="X101" s="87"/>
+      <c r="Y101" s="87"/>
+      <c r="Z101" s="87"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="76"/>
-      <c r="B102" s="76"/>
-      <c r="C102" s="76"/>
-      <c r="D102" s="76"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="76"/>
-      <c r="G102" s="76"/>
-      <c r="H102" s="76"/>
-      <c r="I102" s="76"/>
-      <c r="J102" s="76"/>
-      <c r="K102" s="76"/>
-      <c r="L102" s="76"/>
-      <c r="M102" s="76"/>
-      <c r="N102" s="76"/>
-      <c r="O102" s="76"/>
-      <c r="P102" s="76"/>
-      <c r="Q102" s="76"/>
-      <c r="R102" s="76"/>
-      <c r="S102" s="76"/>
-      <c r="T102" s="76"/>
-      <c r="U102" s="76"/>
-      <c r="V102" s="76"/>
-      <c r="W102" s="76"/>
-      <c r="X102" s="76"/>
-      <c r="Y102" s="76"/>
-      <c r="Z102" s="76"/>
+      <c r="A102" s="87"/>
+      <c r="B102" s="87"/>
+      <c r="C102" s="87"/>
+      <c r="D102" s="87"/>
+      <c r="E102" s="89"/>
+      <c r="F102" s="87"/>
+      <c r="G102" s="87"/>
+      <c r="H102" s="87"/>
+      <c r="I102" s="87"/>
+      <c r="J102" s="87"/>
+      <c r="K102" s="87"/>
+      <c r="L102" s="87"/>
+      <c r="M102" s="87"/>
+      <c r="N102" s="87"/>
+      <c r="O102" s="87"/>
+      <c r="P102" s="87"/>
+      <c r="Q102" s="87"/>
+      <c r="R102" s="87"/>
+      <c r="S102" s="87"/>
+      <c r="T102" s="87"/>
+      <c r="U102" s="87"/>
+      <c r="V102" s="87"/>
+      <c r="W102" s="87"/>
+      <c r="X102" s="87"/>
+      <c r="Y102" s="87"/>
+      <c r="Z102" s="87"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
@@ -5399,25 +5404,25 @@
       <c r="E103" s="3"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
-      <c r="H103" s="76"/>
-      <c r="I103" s="76"/>
-      <c r="J103" s="76"/>
-      <c r="K103" s="76"/>
-      <c r="L103" s="76"/>
-      <c r="M103" s="76"/>
-      <c r="N103" s="76"/>
-      <c r="O103" s="76"/>
-      <c r="P103" s="76"/>
-      <c r="Q103" s="76"/>
-      <c r="R103" s="76"/>
-      <c r="S103" s="76"/>
-      <c r="T103" s="76"/>
-      <c r="U103" s="76"/>
-      <c r="V103" s="76"/>
-      <c r="W103" s="76"/>
-      <c r="X103" s="76"/>
-      <c r="Y103" s="76"/>
-      <c r="Z103" s="76"/>
+      <c r="H103" s="87"/>
+      <c r="I103" s="87"/>
+      <c r="J103" s="87"/>
+      <c r="K103" s="87"/>
+      <c r="L103" s="87"/>
+      <c r="M103" s="87"/>
+      <c r="N103" s="87"/>
+      <c r="O103" s="87"/>
+      <c r="P103" s="87"/>
+      <c r="Q103" s="87"/>
+      <c r="R103" s="87"/>
+      <c r="S103" s="87"/>
+      <c r="T103" s="87"/>
+      <c r="U103" s="87"/>
+      <c r="V103" s="87"/>
+      <c r="W103" s="87"/>
+      <c r="X103" s="87"/>
+      <c r="Y103" s="87"/>
+      <c r="Z103" s="87"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
@@ -11614,13 +11619,13 @@
     <row r="10" ht="27.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="21" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="E10" s="24">
         <v>1.0</v>
@@ -11654,13 +11659,13 @@
     <row r="11" ht="27.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="21" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E11" s="24">
         <f>IF(C11="Simple",1,IF(C11="Intermedio",2,IF(C11="Complejo",3,"error")))</f>
@@ -11696,7 +11701,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="28"/>
       <c r="C12" s="29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -11783,19 +11788,19 @@
     </row>
     <row r="15" ht="27.75" customHeight="1">
       <c r="A15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>27</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>9</v>
@@ -11824,10 +11829,10 @@
     <row r="16" ht="27.75" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="21"/>
-      <c r="D16" s="35">
+      <c r="D16" s="90">
         <v>6.0</v>
       </c>
       <c r="E16" s="24" t="str">
@@ -11842,7 +11847,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="36"/>
+      <c r="K16" s="39"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -11851,7 +11856,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="36"/>
+      <c r="T16" s="39"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -11862,10 +11867,10 @@
     <row r="17" ht="27.75" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="21" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="C17" s="21"/>
-      <c r="D17" s="35">
+      <c r="D17" s="90">
         <v>2.0</v>
       </c>
       <c r="E17" s="24" t="str">
@@ -11880,7 +11885,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="36"/>
+      <c r="K17" s="39"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -11889,7 +11894,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="36"/>
+      <c r="T17" s="39"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -11900,10 +11905,10 @@
     <row r="18" ht="27.75" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38">
+        <v>28</v>
+      </c>
+      <c r="C18" s="49"/>
+      <c r="D18" s="48">
         <v>6.0</v>
       </c>
       <c r="E18" s="24" t="str">
@@ -11918,7 +11923,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="36"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -11927,7 +11932,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="36"/>
+      <c r="T18" s="39"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -11938,14 +11943,14 @@
     <row r="19" ht="27.75" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38">
+        <v>132</v>
+      </c>
+      <c r="C19" s="49"/>
+      <c r="D19" s="48">
         <v>3.0</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F19" s="24">
         <v>5.0</v>
@@ -11954,7 +11959,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="36"/>
+      <c r="K19" s="39"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -11963,7 +11968,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="36"/>
+      <c r="T19" s="39"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -11974,10 +11979,10 @@
     <row r="20" ht="27.75" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38">
+        <v>25</v>
+      </c>
+      <c r="C20" s="49"/>
+      <c r="D20" s="48">
         <v>3.0</v>
       </c>
       <c r="E20" s="24" t="str">
@@ -11992,7 +11997,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="36"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -12001,7 +12006,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="36"/>
+      <c r="T20" s="39"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
@@ -12012,10 +12017,10 @@
     <row r="21" ht="27.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38">
+        <v>133</v>
+      </c>
+      <c r="C21" s="49"/>
+      <c r="D21" s="48">
         <v>3.0</v>
       </c>
       <c r="E21" s="24" t="str">
@@ -12030,7 +12035,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="36"/>
+      <c r="K21" s="39"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -12039,7 +12044,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="36"/>
+      <c r="T21" s="39"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
@@ -12050,10 +12055,10 @@
     <row r="22" ht="27.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38">
+        <v>30</v>
+      </c>
+      <c r="C22" s="49"/>
+      <c r="D22" s="48">
         <v>10.0</v>
       </c>
       <c r="E22" s="24" t="str">
@@ -12068,7 +12073,7 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="36"/>
+      <c r="K22" s="39"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -12077,7 +12082,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="36"/>
+      <c r="T22" s="39"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -12088,14 +12093,14 @@
     <row r="23" ht="27.75" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38">
+        <v>31</v>
+      </c>
+      <c r="C23" s="49"/>
+      <c r="D23" s="48">
         <v>4.0</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F23" s="24">
         <v>10.0</v>
@@ -12104,7 +12109,7 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="36"/>
+      <c r="K23" s="39"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -12113,7 +12118,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="36"/>
+      <c r="T23" s="39"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -12124,10 +12129,10 @@
     <row r="24" ht="27.75" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38">
+        <v>33</v>
+      </c>
+      <c r="C24" s="49"/>
+      <c r="D24" s="48">
         <v>4.0</v>
       </c>
       <c r="E24" s="24" t="str">
@@ -12142,7 +12147,7 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="36"/>
+      <c r="K24" s="39"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -12151,7 +12156,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="36"/>
+      <c r="T24" s="39"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -12162,10 +12167,10 @@
     <row r="25" ht="27.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38">
+        <v>34</v>
+      </c>
+      <c r="C25" s="49"/>
+      <c r="D25" s="48">
         <v>3.0</v>
       </c>
       <c r="E25" s="24" t="str">
@@ -12180,7 +12185,7 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="36"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -12189,7 +12194,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="36"/>
+      <c r="T25" s="39"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -12200,10 +12205,10 @@
     <row r="26" ht="27.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38">
+        <v>35</v>
+      </c>
+      <c r="C26" s="49"/>
+      <c r="D26" s="48">
         <v>3.0</v>
       </c>
       <c r="E26" s="24" t="str">
@@ -12218,7 +12223,7 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="36"/>
+      <c r="K26" s="39"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -12227,7 +12232,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="36"/>
+      <c r="T26" s="39"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -12238,10 +12243,10 @@
     <row r="27" ht="27.75" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C27" s="21"/>
-      <c r="D27" s="38">
+      <c r="D27" s="48">
         <v>4.0</v>
       </c>
       <c r="E27" s="24" t="str">
@@ -12256,7 +12261,7 @@
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="36"/>
+      <c r="K27" s="39"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -12265,7 +12270,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="36"/>
+      <c r="T27" s="39"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -12276,10 +12281,10 @@
     <row r="28" ht="27.75" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38">
+        <v>37</v>
+      </c>
+      <c r="C28" s="49"/>
+      <c r="D28" s="48">
         <v>3.0</v>
       </c>
       <c r="E28" s="24" t="str">
@@ -12294,7 +12299,7 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="36"/>
+      <c r="K28" s="39"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -12303,7 +12308,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="36"/>
+      <c r="T28" s="39"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -12313,13 +12318,13 @@
     </row>
     <row r="29" ht="27.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="43">
+      <c r="B29" s="50"/>
+      <c r="C29" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="52"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54">
         <f>SUM(F16:F28)</f>
         <v>100</v>
       </c>
@@ -12327,7 +12332,7 @@
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="36"/>
+      <c r="K29" s="39"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -12336,7 +12341,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="36"/>
+      <c r="T29" s="39"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -12355,7 +12360,7 @@
       <c r="H30" s="18"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="36"/>
+      <c r="K30" s="39"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -12402,11 +12407,11 @@
     </row>
     <row r="32" ht="27.75" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="44"/>
+        <v>39</v>
+      </c>
+      <c r="B32" s="55"/>
       <c r="C32" s="29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="7"/>
@@ -12493,25 +12498,25 @@
     </row>
     <row r="35" ht="27.75" customHeight="1">
       <c r="A35" s="18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -12535,27 +12540,27 @@
     </row>
     <row r="36" ht="27.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="47">
+      <c r="B36" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="58">
         <v>2.0</v>
       </c>
       <c r="F36" s="25">
         <v>0.0</v>
       </c>
-      <c r="G36" s="48">
+      <c r="G36" s="59">
         <f t="shared" ref="G36:G48" si="7">E36*F36</f>
         <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I36" s="18"/>
       <c r="J36" s="18"/>
@@ -12578,27 +12583,27 @@
     </row>
     <row r="37" ht="27.75" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="45" t="s">
+      <c r="B37" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="48">
+      <c r="E37" s="59">
         <v>2.0</v>
       </c>
       <c r="F37" s="25">
         <v>5.0</v>
       </c>
-      <c r="G37" s="48">
+      <c r="G37" s="59">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="H37" s="50" t="s">
-        <v>57</v>
+      <c r="H37" s="61" t="s">
+        <v>53</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -12621,20 +12626,20 @@
     </row>
     <row r="38" ht="27.0" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="48">
+      <c r="B38" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="60"/>
+      <c r="E38" s="59">
         <v>1.0</v>
       </c>
       <c r="F38" s="25">
         <v>5.0</v>
       </c>
-      <c r="G38" s="48">
+      <c r="G38" s="59">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
@@ -12660,22 +12665,22 @@
     </row>
     <row r="39" ht="27.75" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="48">
+      <c r="B39" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="59">
         <v>1.0</v>
       </c>
       <c r="F39" s="25">
         <v>3.0</v>
       </c>
-      <c r="G39" s="48">
+      <c r="G39" s="59">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
@@ -12701,22 +12706,22 @@
     </row>
     <row r="40" ht="30.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="47">
+      <c r="B40" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="58">
         <v>1.0</v>
       </c>
       <c r="F40" s="25">
         <v>0.0</v>
       </c>
-      <c r="G40" s="48">
+      <c r="G40" s="59">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -12742,22 +12747,22 @@
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="E41" s="47">
+      <c r="B41" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="58">
         <v>0.5</v>
       </c>
       <c r="F41" s="25">
         <v>3.0</v>
       </c>
-      <c r="G41" s="48">
+      <c r="G41" s="59">
         <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
@@ -12783,22 +12788,22 @@
     </row>
     <row r="42" ht="27.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="47">
+      <c r="B42" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="58">
         <v>0.5</v>
       </c>
       <c r="F42" s="25">
         <v>5.0</v>
       </c>
-      <c r="G42" s="48">
+      <c r="G42" s="59">
         <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
@@ -12824,22 +12829,22 @@
     </row>
     <row r="43" ht="27.75" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="47">
+      <c r="B43" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="58">
         <v>2.0</v>
       </c>
       <c r="F43" s="25">
         <v>3.0</v>
       </c>
-      <c r="G43" s="48">
+      <c r="G43" s="59">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
@@ -12865,22 +12870,22 @@
     </row>
     <row r="44" ht="27.75" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="47">
+      <c r="B44" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="58">
         <v>1.0</v>
       </c>
       <c r="F44" s="25">
         <v>0.0</v>
       </c>
-      <c r="G44" s="48">
+      <c r="G44" s="59">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -12906,20 +12911,20 @@
     </row>
     <row r="45" ht="27.75" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="46"/>
-      <c r="E45" s="47">
+      <c r="B45" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="57"/>
+      <c r="E45" s="58">
         <v>1.0</v>
       </c>
       <c r="F45" s="25">
         <v>5.0</v>
       </c>
-      <c r="G45" s="48">
+      <c r="G45" s="59">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
@@ -12945,22 +12950,22 @@
     </row>
     <row r="46" ht="27.75" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="48">
+      <c r="B46" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="59">
         <v>1.0</v>
       </c>
       <c r="F46" s="25">
         <v>5.0</v>
       </c>
-      <c r="G46" s="48">
+      <c r="G46" s="59">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
@@ -12986,22 +12991,22 @@
     </row>
     <row r="47" ht="30.75" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="48">
+      <c r="B47" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="59">
         <v>1.0</v>
       </c>
       <c r="F47" s="25">
         <v>5.0</v>
       </c>
-      <c r="G47" s="48">
+      <c r="G47" s="59">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
@@ -13027,22 +13032,22 @@
     </row>
     <row r="48" ht="31.5" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="47">
+      <c r="B48" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="58">
         <v>1.0</v>
       </c>
       <c r="F48" s="25">
         <v>4.0</v>
       </c>
-      <c r="G48" s="48">
+      <c r="G48" s="59">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
@@ -13069,13 +13074,13 @@
     <row r="49" ht="30.75" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="7"/>
-      <c r="G49" s="51">
+      <c r="G49" s="62">
         <f>SUM(G36:G48)</f>
         <v>47</v>
       </c>
@@ -13102,13 +13107,13 @@
     <row r="50" ht="27.75" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
-      <c r="G50" s="43">
+      <c r="G50" s="54">
         <f>0.6+(0.01*G49)</f>
         <v>1.07</v>
       </c>
@@ -13162,12 +13167,12 @@
     </row>
     <row r="52" ht="27.75" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -13190,25 +13195,25 @@
     </row>
     <row r="53" ht="27.75" customHeight="1">
       <c r="A53" s="18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G53" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -13232,27 +13237,27 @@
     </row>
     <row r="54" ht="64.5" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D54" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="47">
+      <c r="B54" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="58">
         <v>1.5</v>
       </c>
       <c r="F54" s="25">
         <v>3.0</v>
       </c>
-      <c r="G54" s="48">
+      <c r="G54" s="59">
         <f t="shared" ref="G54:G61" si="8">E54*F54</f>
         <v>4.5</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I54" s="18"/>
       <c r="J54" s="18"/>
@@ -13275,27 +13280,27 @@
     </row>
     <row r="55" ht="51.0" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="45" t="s">
+      <c r="B55" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="D55" s="49" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" s="47">
+      <c r="E55" s="58">
         <v>0.5</v>
       </c>
-      <c r="F55" s="55">
+      <c r="F55" s="66">
         <v>4.0</v>
       </c>
-      <c r="G55" s="48">
+      <c r="G55" s="59">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="H55" s="50" t="s">
-        <v>57</v>
+      <c r="H55" s="61" t="s">
+        <v>53</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -13318,22 +13323,22 @@
     </row>
     <row r="56" ht="48.75" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D56" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="E56" s="47">
+      <c r="B56" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="E56" s="58">
         <v>1.0</v>
       </c>
       <c r="F56" s="25">
         <v>4.0</v>
       </c>
-      <c r="G56" s="48">
+      <c r="G56" s="59">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
@@ -13359,22 +13364,22 @@
     </row>
     <row r="57" ht="46.5" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="E57" s="47">
+      <c r="B57" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="58">
         <v>0.5</v>
       </c>
       <c r="F57" s="25">
         <v>3.0</v>
       </c>
-      <c r="G57" s="48">
+      <c r="G57" s="59">
         <f t="shared" si="8"/>
         <v>1.5</v>
       </c>
@@ -13400,22 +13405,22 @@
     </row>
     <row r="58" ht="37.5" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D58" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E58" s="47">
+      <c r="B58" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="58">
         <v>1.0</v>
       </c>
       <c r="F58" s="25">
         <v>4.0</v>
       </c>
-      <c r="G58" s="48">
+      <c r="G58" s="59">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
@@ -13441,22 +13446,22 @@
     </row>
     <row r="59" ht="43.5" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="E59" s="47">
+      <c r="B59" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="C59" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="D59" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" s="58">
         <v>2.0</v>
       </c>
       <c r="F59" s="25">
         <v>2.0</v>
       </c>
-      <c r="G59" s="48">
+      <c r="G59" s="59">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
@@ -13482,22 +13487,22 @@
     </row>
     <row r="60" ht="71.25" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="C60" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D60" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="E60" s="47">
+      <c r="B60" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="58">
         <v>-1.0</v>
       </c>
       <c r="F60" s="25">
         <v>4.0</v>
       </c>
-      <c r="G60" s="48">
+      <c r="G60" s="59">
         <f t="shared" si="8"/>
         <v>-4</v>
       </c>
@@ -13523,22 +13528,22 @@
     </row>
     <row r="61" ht="62.25" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="C61" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="D61" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="E61" s="47">
+      <c r="B61" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="58">
         <v>-1.0</v>
       </c>
-      <c r="F61" s="55">
+      <c r="F61" s="66">
         <v>4.0</v>
       </c>
-      <c r="G61" s="48">
+      <c r="G61" s="59">
         <f t="shared" si="8"/>
         <v>-4</v>
       </c>
@@ -13565,7 +13570,7 @@
     <row r="62" ht="38.25" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="29" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -13598,7 +13603,7 @@
     <row r="63" ht="27.75" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -13631,11 +13636,11 @@
     <row r="64" ht="27.75" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="29"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="59" t="s">
-        <v>108</v>
+      <c r="C64" s="68"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="70" t="s">
+        <v>104</v>
       </c>
       <c r="G64" s="19">
         <f>COUNTIF($F$54:$F$59,"&lt;3")+COUNTIF($F$60:$F$61,"&gt;3")</f>
@@ -13719,16 +13724,16 @@
     </row>
     <row r="67" ht="27.75" customHeight="1">
       <c r="A67" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B67" s="60" t="s">
-        <v>136</v>
+        <v>105</v>
+      </c>
+      <c r="B67" s="71" t="s">
+        <v>137</v>
       </c>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="7"/>
-      <c r="G67" s="61">
+      <c r="G67" s="72">
         <f>F32*G50*G63</f>
         <v>115.7312</v>
       </c>
@@ -13809,22 +13814,22 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" ht="27.75" customHeight="1">
-      <c r="A70" s="62" t="s">
-        <v>111</v>
+      <c r="A70" s="73" t="s">
+        <v>107</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="1"/>
       <c r="G70" s="20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -13848,20 +13853,20 @@
     </row>
     <row r="71" ht="31.5" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="63">
+      <c r="B71" s="74">
         <v>20.0</v>
       </c>
-      <c r="C71" s="63">
+      <c r="C71" s="74">
         <f>IF($G$64&gt;=5,36,IF(AND(G$64&gt;2,$G$64&lt;=4),28, IF(AND($G$64&gt;=0,$G$64&lt;=2),20,"error")))</f>
         <v>28</v>
       </c>
-      <c r="D71" s="64">
+      <c r="D71" s="75">
         <f>IF($G$64&gt;=5,$G$71*(36/20),IF(AND($G$64&gt;2,$G$64&lt;=4),$G$71*(28/20), IF(AND($G$64&gt;=0,$G$64&lt;=2),$G$71,"error")))</f>
         <v>2.8</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="79">
+      <c r="G71" s="91">
         <v>2.0</v>
       </c>
       <c r="H71" s="1"/>
@@ -13886,8 +13891,8 @@
     </row>
     <row r="72" ht="27.75" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="66" t="s">
-        <v>116</v>
+      <c r="B72" s="77" t="s">
+        <v>112</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="7"/>
@@ -13915,18 +13920,18 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" ht="27.75" customHeight="1">
-      <c r="A73" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B73" s="63">
+      <c r="A73" s="78" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73" s="74">
         <f t="shared" ref="B73:D73" si="9">$G$67*B71</f>
         <v>2314.624</v>
       </c>
-      <c r="C73" s="63">
+      <c r="C73" s="74">
         <f t="shared" si="9"/>
         <v>3240.4736</v>
       </c>
-      <c r="D73" s="63">
+      <c r="D73" s="74">
         <f t="shared" si="9"/>
         <v>324.04736</v>
       </c>
@@ -13954,18 +13959,18 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" ht="27.75" customHeight="1">
-      <c r="A74" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="B74" s="68">
+      <c r="A74" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="B74" s="79">
         <f t="shared" ref="B74:C74" si="10">B73/(22*8)</f>
         <v>13.15127273</v>
       </c>
-      <c r="C74" s="68">
+      <c r="C74" s="79">
         <f t="shared" si="10"/>
         <v>18.41178182</v>
       </c>
-      <c r="D74" s="69">
+      <c r="D74" s="80">
         <f>D73/(22*3)</f>
         <v>4.909808485</v>
       </c>
@@ -14050,15 +14055,15 @@
     </row>
     <row r="77" ht="27.75" customHeight="1">
       <c r="A77" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B77" s="70" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="71"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="57"/>
-      <c r="F77" s="72"/>
+        <v>115</v>
+      </c>
+      <c r="B77" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" s="82"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="68"/>
+      <c r="F77" s="83"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -14082,20 +14087,20 @@
     </row>
     <row r="78" ht="27.75" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="44" t="s">
+      <c r="B78" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D78" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="E78" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="F78" s="72" t="s">
         <v>121</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D78" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="E78" s="61" t="s">
-        <v>124</v>
-      </c>
-      <c r="F78" s="61" t="s">
-        <v>125</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -14120,21 +14125,21 @@
     </row>
     <row r="79" ht="27.75" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="C79" s="74">
+      <c r="B79" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="C79" s="85">
         <v>0.4</v>
       </c>
-      <c r="D79" s="68">
+      <c r="D79" s="79">
         <f t="shared" ref="D79:F79" si="11">$C79/$C$79*B$74</f>
         <v>13.15127273</v>
       </c>
-      <c r="E79" s="68">
+      <c r="E79" s="79">
         <f t="shared" si="11"/>
         <v>18.41178182</v>
       </c>
-      <c r="F79" s="68">
+      <c r="F79" s="79">
         <f t="shared" si="11"/>
         <v>4.909808485</v>
       </c>
@@ -14161,22 +14166,22 @@
     </row>
     <row r="80" ht="27.75" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="C80" s="74">
+      <c r="B80" s="84" t="s">
+        <v>123</v>
+      </c>
+      <c r="C80" s="85">
         <f>1-C79</f>
         <v>0.6</v>
       </c>
-      <c r="D80" s="63">
+      <c r="D80" s="74">
         <f t="shared" ref="D80:F80" si="12">$C80/$C$79*B$74</f>
         <v>19.72690909</v>
       </c>
-      <c r="E80" s="63">
+      <c r="E80" s="74">
         <f t="shared" si="12"/>
         <v>27.61767273</v>
       </c>
-      <c r="F80" s="63">
+      <c r="F80" s="74">
         <f t="shared" si="12"/>
         <v>7.364712727</v>
       </c>
@@ -14203,20 +14208,20 @@
     </row>
     <row r="81" ht="27.75" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="75"/>
-      <c r="C81" s="74">
+      <c r="B81" s="86"/>
+      <c r="C81" s="85">
         <f>SUM(C79:C80)</f>
         <v>1</v>
       </c>
-      <c r="D81" s="68">
+      <c r="D81" s="79">
         <f t="shared" ref="D81:F81" si="13">$C81/$C$79*B$74</f>
         <v>32.87818182</v>
       </c>
-      <c r="E81" s="68">
+      <c r="E81" s="79">
         <f t="shared" si="13"/>
         <v>46.02945455</v>
       </c>
-      <c r="F81" s="68">
+      <c r="F81" s="79">
         <f t="shared" si="13"/>
         <v>12.27452121</v>
       </c>
@@ -14271,7 +14276,7 @@
     </row>
     <row r="83" ht="27.75" customHeight="1">
       <c r="A83" s="18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B83" s="25">
         <v>5.0</v>
@@ -14331,16 +14336,16 @@
     </row>
     <row r="85" ht="27.75" customHeight="1">
       <c r="A85" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="B85" s="61" t="s">
-        <v>130</v>
-      </c>
-      <c r="C85" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="D85" s="61" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="B85" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="D85" s="72" t="s">
+        <v>128</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="1"/>
@@ -14366,22 +14371,22 @@
       <c r="Z85" s="1"/>
     </row>
     <row r="86" ht="27.75" customHeight="1">
-      <c r="A86" s="76"/>
-      <c r="B86" s="77">
+      <c r="A86" s="87"/>
+      <c r="B86" s="88">
         <f>$D$81/$B$83</f>
         <v>6.575636364</v>
       </c>
-      <c r="C86" s="77">
+      <c r="C86" s="88">
         <f>$E$81/$B$83</f>
         <v>9.205890909</v>
       </c>
-      <c r="D86" s="77">
+      <c r="D86" s="88">
         <f>$F$81/$B$83</f>
         <v>2.454904242</v>
       </c>
-      <c r="E86" s="76"/>
-      <c r="F86" s="76"/>
-      <c r="G86" s="76"/>
+      <c r="E86" s="87"/>
+      <c r="F86" s="87"/>
+      <c r="G86" s="87"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -14403,452 +14408,452 @@
       <c r="Z86" s="1"/>
     </row>
     <row r="87" ht="27.75" customHeight="1">
-      <c r="A87" s="76"/>
-      <c r="B87" s="76"/>
-      <c r="C87" s="76"/>
-      <c r="D87" s="76"/>
-      <c r="E87" s="78"/>
-      <c r="F87" s="76"/>
-      <c r="G87" s="76"/>
-      <c r="H87" s="76"/>
-      <c r="I87" s="76"/>
-      <c r="J87" s="76"/>
-      <c r="K87" s="76"/>
-      <c r="L87" s="76"/>
-      <c r="M87" s="76"/>
-      <c r="N87" s="76"/>
-      <c r="O87" s="76"/>
-      <c r="P87" s="76"/>
-      <c r="Q87" s="76"/>
-      <c r="R87" s="76"/>
-      <c r="S87" s="76"/>
-      <c r="T87" s="76"/>
-      <c r="U87" s="76"/>
-      <c r="V87" s="76"/>
-      <c r="W87" s="76"/>
-      <c r="X87" s="76"/>
-      <c r="Y87" s="76"/>
-      <c r="Z87" s="76"/>
+      <c r="A87" s="87"/>
+      <c r="B87" s="87"/>
+      <c r="C87" s="87"/>
+      <c r="D87" s="87"/>
+      <c r="E87" s="89"/>
+      <c r="F87" s="87"/>
+      <c r="G87" s="87"/>
+      <c r="H87" s="87"/>
+      <c r="I87" s="87"/>
+      <c r="J87" s="87"/>
+      <c r="K87" s="87"/>
+      <c r="L87" s="87"/>
+      <c r="M87" s="87"/>
+      <c r="N87" s="87"/>
+      <c r="O87" s="87"/>
+      <c r="P87" s="87"/>
+      <c r="Q87" s="87"/>
+      <c r="R87" s="87"/>
+      <c r="S87" s="87"/>
+      <c r="T87" s="87"/>
+      <c r="U87" s="87"/>
+      <c r="V87" s="87"/>
+      <c r="W87" s="87"/>
+      <c r="X87" s="87"/>
+      <c r="Y87" s="87"/>
+      <c r="Z87" s="87"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="76"/>
-      <c r="B88" s="76"/>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="78"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="76"/>
-      <c r="H88" s="76"/>
-      <c r="I88" s="76"/>
-      <c r="J88" s="76"/>
-      <c r="K88" s="76"/>
-      <c r="L88" s="76"/>
-      <c r="M88" s="76"/>
-      <c r="N88" s="76"/>
-      <c r="O88" s="76"/>
-      <c r="P88" s="76"/>
-      <c r="Q88" s="76"/>
-      <c r="R88" s="76"/>
-      <c r="S88" s="76"/>
-      <c r="T88" s="76"/>
-      <c r="U88" s="76"/>
-      <c r="V88" s="76"/>
-      <c r="W88" s="76"/>
-      <c r="X88" s="76"/>
-      <c r="Y88" s="76"/>
-      <c r="Z88" s="76"/>
+      <c r="A88" s="87"/>
+      <c r="B88" s="87"/>
+      <c r="C88" s="87"/>
+      <c r="D88" s="87"/>
+      <c r="E88" s="89"/>
+      <c r="F88" s="87"/>
+      <c r="G88" s="87"/>
+      <c r="H88" s="87"/>
+      <c r="I88" s="87"/>
+      <c r="J88" s="87"/>
+      <c r="K88" s="87"/>
+      <c r="L88" s="87"/>
+      <c r="M88" s="87"/>
+      <c r="N88" s="87"/>
+      <c r="O88" s="87"/>
+      <c r="P88" s="87"/>
+      <c r="Q88" s="87"/>
+      <c r="R88" s="87"/>
+      <c r="S88" s="87"/>
+      <c r="T88" s="87"/>
+      <c r="U88" s="87"/>
+      <c r="V88" s="87"/>
+      <c r="W88" s="87"/>
+      <c r="X88" s="87"/>
+      <c r="Y88" s="87"/>
+      <c r="Z88" s="87"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="76"/>
-      <c r="B89" s="76"/>
-      <c r="C89" s="76"/>
-      <c r="D89" s="76"/>
-      <c r="E89" s="78"/>
-      <c r="F89" s="76"/>
-      <c r="G89" s="76"/>
-      <c r="H89" s="76"/>
-      <c r="I89" s="76"/>
-      <c r="J89" s="76"/>
-      <c r="K89" s="76"/>
-      <c r="L89" s="76"/>
-      <c r="M89" s="76"/>
-      <c r="N89" s="76"/>
-      <c r="O89" s="76"/>
-      <c r="P89" s="76"/>
-      <c r="Q89" s="76"/>
-      <c r="R89" s="76"/>
-      <c r="S89" s="76"/>
-      <c r="T89" s="76"/>
-      <c r="U89" s="76"/>
-      <c r="V89" s="76"/>
-      <c r="W89" s="76"/>
-      <c r="X89" s="76"/>
-      <c r="Y89" s="76"/>
-      <c r="Z89" s="76"/>
+      <c r="A89" s="87"/>
+      <c r="B89" s="87"/>
+      <c r="C89" s="87"/>
+      <c r="D89" s="87"/>
+      <c r="E89" s="89"/>
+      <c r="F89" s="87"/>
+      <c r="G89" s="87"/>
+      <c r="H89" s="87"/>
+      <c r="I89" s="87"/>
+      <c r="J89" s="87"/>
+      <c r="K89" s="87"/>
+      <c r="L89" s="87"/>
+      <c r="M89" s="87"/>
+      <c r="N89" s="87"/>
+      <c r="O89" s="87"/>
+      <c r="P89" s="87"/>
+      <c r="Q89" s="87"/>
+      <c r="R89" s="87"/>
+      <c r="S89" s="87"/>
+      <c r="T89" s="87"/>
+      <c r="U89" s="87"/>
+      <c r="V89" s="87"/>
+      <c r="W89" s="87"/>
+      <c r="X89" s="87"/>
+      <c r="Y89" s="87"/>
+      <c r="Z89" s="87"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="76"/>
-      <c r="B90" s="76"/>
-      <c r="C90" s="76"/>
-      <c r="D90" s="76"/>
-      <c r="E90" s="78"/>
-      <c r="F90" s="76"/>
-      <c r="G90" s="76"/>
-      <c r="H90" s="76"/>
-      <c r="I90" s="76"/>
-      <c r="J90" s="76"/>
-      <c r="K90" s="76"/>
-      <c r="L90" s="76"/>
-      <c r="M90" s="76"/>
-      <c r="N90" s="76"/>
-      <c r="O90" s="76"/>
-      <c r="P90" s="76"/>
-      <c r="Q90" s="76"/>
-      <c r="R90" s="76"/>
-      <c r="S90" s="76"/>
-      <c r="T90" s="76"/>
-      <c r="U90" s="76"/>
-      <c r="V90" s="76"/>
-      <c r="W90" s="76"/>
-      <c r="X90" s="76"/>
-      <c r="Y90" s="76"/>
-      <c r="Z90" s="76"/>
+      <c r="A90" s="87"/>
+      <c r="B90" s="87"/>
+      <c r="C90" s="87"/>
+      <c r="D90" s="87"/>
+      <c r="E90" s="89"/>
+      <c r="F90" s="87"/>
+      <c r="G90" s="87"/>
+      <c r="H90" s="87"/>
+      <c r="I90" s="87"/>
+      <c r="J90" s="87"/>
+      <c r="K90" s="87"/>
+      <c r="L90" s="87"/>
+      <c r="M90" s="87"/>
+      <c r="N90" s="87"/>
+      <c r="O90" s="87"/>
+      <c r="P90" s="87"/>
+      <c r="Q90" s="87"/>
+      <c r="R90" s="87"/>
+      <c r="S90" s="87"/>
+      <c r="T90" s="87"/>
+      <c r="U90" s="87"/>
+      <c r="V90" s="87"/>
+      <c r="W90" s="87"/>
+      <c r="X90" s="87"/>
+      <c r="Y90" s="87"/>
+      <c r="Z90" s="87"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="76"/>
-      <c r="B91" s="76"/>
-      <c r="C91" s="76"/>
-      <c r="D91" s="76"/>
-      <c r="E91" s="78"/>
-      <c r="F91" s="76"/>
-      <c r="G91" s="76"/>
-      <c r="H91" s="76"/>
-      <c r="I91" s="76"/>
-      <c r="J91" s="76"/>
-      <c r="K91" s="76"/>
-      <c r="L91" s="76"/>
-      <c r="M91" s="76"/>
-      <c r="N91" s="76"/>
-      <c r="O91" s="76"/>
-      <c r="P91" s="76"/>
-      <c r="Q91" s="76"/>
-      <c r="R91" s="76"/>
-      <c r="S91" s="76"/>
-      <c r="T91" s="76"/>
-      <c r="U91" s="76"/>
-      <c r="V91" s="76"/>
-      <c r="W91" s="76"/>
-      <c r="X91" s="76"/>
-      <c r="Y91" s="76"/>
-      <c r="Z91" s="76"/>
+      <c r="A91" s="87"/>
+      <c r="B91" s="87"/>
+      <c r="C91" s="87"/>
+      <c r="D91" s="87"/>
+      <c r="E91" s="89"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="87"/>
+      <c r="I91" s="87"/>
+      <c r="J91" s="87"/>
+      <c r="K91" s="87"/>
+      <c r="L91" s="87"/>
+      <c r="M91" s="87"/>
+      <c r="N91" s="87"/>
+      <c r="O91" s="87"/>
+      <c r="P91" s="87"/>
+      <c r="Q91" s="87"/>
+      <c r="R91" s="87"/>
+      <c r="S91" s="87"/>
+      <c r="T91" s="87"/>
+      <c r="U91" s="87"/>
+      <c r="V91" s="87"/>
+      <c r="W91" s="87"/>
+      <c r="X91" s="87"/>
+      <c r="Y91" s="87"/>
+      <c r="Z91" s="87"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="76"/>
-      <c r="B92" s="76"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
-      <c r="E92" s="78"/>
-      <c r="F92" s="76"/>
-      <c r="G92" s="76"/>
-      <c r="H92" s="76"/>
-      <c r="I92" s="76"/>
-      <c r="J92" s="76"/>
-      <c r="K92" s="76"/>
-      <c r="L92" s="76"/>
-      <c r="M92" s="76"/>
-      <c r="N92" s="76"/>
-      <c r="O92" s="76"/>
-      <c r="P92" s="76"/>
-      <c r="Q92" s="76"/>
-      <c r="R92" s="76"/>
-      <c r="S92" s="76"/>
-      <c r="T92" s="76"/>
-      <c r="U92" s="76"/>
-      <c r="V92" s="76"/>
-      <c r="W92" s="76"/>
-      <c r="X92" s="76"/>
-      <c r="Y92" s="76"/>
-      <c r="Z92" s="76"/>
+      <c r="A92" s="87"/>
+      <c r="B92" s="87"/>
+      <c r="C92" s="87"/>
+      <c r="D92" s="87"/>
+      <c r="E92" s="89"/>
+      <c r="F92" s="87"/>
+      <c r="G92" s="87"/>
+      <c r="H92" s="87"/>
+      <c r="I92" s="87"/>
+      <c r="J92" s="87"/>
+      <c r="K92" s="87"/>
+      <c r="L92" s="87"/>
+      <c r="M92" s="87"/>
+      <c r="N92" s="87"/>
+      <c r="O92" s="87"/>
+      <c r="P92" s="87"/>
+      <c r="Q92" s="87"/>
+      <c r="R92" s="87"/>
+      <c r="S92" s="87"/>
+      <c r="T92" s="87"/>
+      <c r="U92" s="87"/>
+      <c r="V92" s="87"/>
+      <c r="W92" s="87"/>
+      <c r="X92" s="87"/>
+      <c r="Y92" s="87"/>
+      <c r="Z92" s="87"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="76"/>
-      <c r="B93" s="76"/>
-      <c r="C93" s="76"/>
-      <c r="D93" s="76"/>
-      <c r="E93" s="78"/>
-      <c r="F93" s="76"/>
-      <c r="G93" s="76"/>
-      <c r="H93" s="76"/>
-      <c r="I93" s="76"/>
-      <c r="J93" s="76"/>
-      <c r="K93" s="76"/>
-      <c r="L93" s="76"/>
-      <c r="M93" s="76"/>
-      <c r="N93" s="76"/>
-      <c r="O93" s="76"/>
-      <c r="P93" s="76"/>
-      <c r="Q93" s="76"/>
-      <c r="R93" s="76"/>
-      <c r="S93" s="76"/>
-      <c r="T93" s="76"/>
-      <c r="U93" s="76"/>
-      <c r="V93" s="76"/>
-      <c r="W93" s="76"/>
-      <c r="X93" s="76"/>
-      <c r="Y93" s="76"/>
-      <c r="Z93" s="76"/>
+      <c r="A93" s="87"/>
+      <c r="B93" s="87"/>
+      <c r="C93" s="87"/>
+      <c r="D93" s="87"/>
+      <c r="E93" s="89"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="87"/>
+      <c r="I93" s="87"/>
+      <c r="J93" s="87"/>
+      <c r="K93" s="87"/>
+      <c r="L93" s="87"/>
+      <c r="M93" s="87"/>
+      <c r="N93" s="87"/>
+      <c r="O93" s="87"/>
+      <c r="P93" s="87"/>
+      <c r="Q93" s="87"/>
+      <c r="R93" s="87"/>
+      <c r="S93" s="87"/>
+      <c r="T93" s="87"/>
+      <c r="U93" s="87"/>
+      <c r="V93" s="87"/>
+      <c r="W93" s="87"/>
+      <c r="X93" s="87"/>
+      <c r="Y93" s="87"/>
+      <c r="Z93" s="87"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="76"/>
-      <c r="B94" s="76"/>
-      <c r="C94" s="76"/>
-      <c r="D94" s="76"/>
-      <c r="E94" s="78"/>
-      <c r="F94" s="76"/>
-      <c r="G94" s="76"/>
-      <c r="H94" s="76"/>
-      <c r="I94" s="76"/>
-      <c r="J94" s="76"/>
-      <c r="K94" s="76"/>
-      <c r="L94" s="76"/>
-      <c r="M94" s="76"/>
-      <c r="N94" s="76"/>
-      <c r="O94" s="76"/>
-      <c r="P94" s="76"/>
-      <c r="Q94" s="76"/>
-      <c r="R94" s="76"/>
-      <c r="S94" s="76"/>
-      <c r="T94" s="76"/>
-      <c r="U94" s="76"/>
-      <c r="V94" s="76"/>
-      <c r="W94" s="76"/>
-      <c r="X94" s="76"/>
-      <c r="Y94" s="76"/>
-      <c r="Z94" s="76"/>
+      <c r="A94" s="87"/>
+      <c r="B94" s="87"/>
+      <c r="C94" s="87"/>
+      <c r="D94" s="87"/>
+      <c r="E94" s="89"/>
+      <c r="F94" s="87"/>
+      <c r="G94" s="87"/>
+      <c r="H94" s="87"/>
+      <c r="I94" s="87"/>
+      <c r="J94" s="87"/>
+      <c r="K94" s="87"/>
+      <c r="L94" s="87"/>
+      <c r="M94" s="87"/>
+      <c r="N94" s="87"/>
+      <c r="O94" s="87"/>
+      <c r="P94" s="87"/>
+      <c r="Q94" s="87"/>
+      <c r="R94" s="87"/>
+      <c r="S94" s="87"/>
+      <c r="T94" s="87"/>
+      <c r="U94" s="87"/>
+      <c r="V94" s="87"/>
+      <c r="W94" s="87"/>
+      <c r="X94" s="87"/>
+      <c r="Y94" s="87"/>
+      <c r="Z94" s="87"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="76"/>
-      <c r="B95" s="76"/>
-      <c r="C95" s="76"/>
-      <c r="D95" s="76"/>
-      <c r="E95" s="78"/>
-      <c r="F95" s="76"/>
-      <c r="G95" s="76"/>
-      <c r="H95" s="76"/>
-      <c r="I95" s="76"/>
-      <c r="J95" s="76"/>
-      <c r="K95" s="76"/>
-      <c r="L95" s="76"/>
-      <c r="M95" s="76"/>
-      <c r="N95" s="76"/>
-      <c r="O95" s="76"/>
-      <c r="P95" s="76"/>
-      <c r="Q95" s="76"/>
-      <c r="R95" s="76"/>
-      <c r="S95" s="76"/>
-      <c r="T95" s="76"/>
-      <c r="U95" s="76"/>
-      <c r="V95" s="76"/>
-      <c r="W95" s="76"/>
-      <c r="X95" s="76"/>
-      <c r="Y95" s="76"/>
-      <c r="Z95" s="76"/>
+      <c r="A95" s="87"/>
+      <c r="B95" s="87"/>
+      <c r="C95" s="87"/>
+      <c r="D95" s="87"/>
+      <c r="E95" s="89"/>
+      <c r="F95" s="87"/>
+      <c r="G95" s="87"/>
+      <c r="H95" s="87"/>
+      <c r="I95" s="87"/>
+      <c r="J95" s="87"/>
+      <c r="K95" s="87"/>
+      <c r="L95" s="87"/>
+      <c r="M95" s="87"/>
+      <c r="N95" s="87"/>
+      <c r="O95" s="87"/>
+      <c r="P95" s="87"/>
+      <c r="Q95" s="87"/>
+      <c r="R95" s="87"/>
+      <c r="S95" s="87"/>
+      <c r="T95" s="87"/>
+      <c r="U95" s="87"/>
+      <c r="V95" s="87"/>
+      <c r="W95" s="87"/>
+      <c r="X95" s="87"/>
+      <c r="Y95" s="87"/>
+      <c r="Z95" s="87"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="76"/>
-      <c r="B96" s="76"/>
-      <c r="C96" s="76"/>
-      <c r="D96" s="76"/>
-      <c r="E96" s="78"/>
-      <c r="F96" s="76"/>
-      <c r="G96" s="76"/>
-      <c r="H96" s="76"/>
-      <c r="I96" s="76"/>
-      <c r="J96" s="76"/>
-      <c r="K96" s="76"/>
-      <c r="L96" s="76"/>
-      <c r="M96" s="76"/>
-      <c r="N96" s="76"/>
-      <c r="O96" s="76"/>
-      <c r="P96" s="76"/>
-      <c r="Q96" s="76"/>
-      <c r="R96" s="76"/>
-      <c r="S96" s="76"/>
-      <c r="T96" s="76"/>
-      <c r="U96" s="76"/>
-      <c r="V96" s="76"/>
-      <c r="W96" s="76"/>
-      <c r="X96" s="76"/>
-      <c r="Y96" s="76"/>
-      <c r="Z96" s="76"/>
+      <c r="A96" s="87"/>
+      <c r="B96" s="87"/>
+      <c r="C96" s="87"/>
+      <c r="D96" s="87"/>
+      <c r="E96" s="89"/>
+      <c r="F96" s="87"/>
+      <c r="G96" s="87"/>
+      <c r="H96" s="87"/>
+      <c r="I96" s="87"/>
+      <c r="J96" s="87"/>
+      <c r="K96" s="87"/>
+      <c r="L96" s="87"/>
+      <c r="M96" s="87"/>
+      <c r="N96" s="87"/>
+      <c r="O96" s="87"/>
+      <c r="P96" s="87"/>
+      <c r="Q96" s="87"/>
+      <c r="R96" s="87"/>
+      <c r="S96" s="87"/>
+      <c r="T96" s="87"/>
+      <c r="U96" s="87"/>
+      <c r="V96" s="87"/>
+      <c r="W96" s="87"/>
+      <c r="X96" s="87"/>
+      <c r="Y96" s="87"/>
+      <c r="Z96" s="87"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="76"/>
-      <c r="B97" s="76"/>
-      <c r="C97" s="76"/>
-      <c r="D97" s="76"/>
-      <c r="E97" s="78"/>
-      <c r="F97" s="76"/>
-      <c r="G97" s="76"/>
-      <c r="H97" s="76"/>
-      <c r="I97" s="76"/>
-      <c r="J97" s="76"/>
-      <c r="K97" s="76"/>
-      <c r="L97" s="76"/>
-      <c r="M97" s="76"/>
-      <c r="N97" s="76"/>
-      <c r="O97" s="76"/>
-      <c r="P97" s="76"/>
-      <c r="Q97" s="76"/>
-      <c r="R97" s="76"/>
-      <c r="S97" s="76"/>
-      <c r="T97" s="76"/>
-      <c r="U97" s="76"/>
-      <c r="V97" s="76"/>
-      <c r="W97" s="76"/>
-      <c r="X97" s="76"/>
-      <c r="Y97" s="76"/>
-      <c r="Z97" s="76"/>
+      <c r="A97" s="87"/>
+      <c r="B97" s="87"/>
+      <c r="C97" s="87"/>
+      <c r="D97" s="87"/>
+      <c r="E97" s="89"/>
+      <c r="F97" s="87"/>
+      <c r="G97" s="87"/>
+      <c r="H97" s="87"/>
+      <c r="I97" s="87"/>
+      <c r="J97" s="87"/>
+      <c r="K97" s="87"/>
+      <c r="L97" s="87"/>
+      <c r="M97" s="87"/>
+      <c r="N97" s="87"/>
+      <c r="O97" s="87"/>
+      <c r="P97" s="87"/>
+      <c r="Q97" s="87"/>
+      <c r="R97" s="87"/>
+      <c r="S97" s="87"/>
+      <c r="T97" s="87"/>
+      <c r="U97" s="87"/>
+      <c r="V97" s="87"/>
+      <c r="W97" s="87"/>
+      <c r="X97" s="87"/>
+      <c r="Y97" s="87"/>
+      <c r="Z97" s="87"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="76"/>
-      <c r="B98" s="76"/>
-      <c r="C98" s="76"/>
-      <c r="D98" s="76"/>
-      <c r="E98" s="78"/>
-      <c r="F98" s="76"/>
-      <c r="G98" s="76"/>
-      <c r="H98" s="76"/>
-      <c r="I98" s="76"/>
-      <c r="J98" s="76"/>
-      <c r="K98" s="76"/>
-      <c r="L98" s="76"/>
-      <c r="M98" s="76"/>
-      <c r="N98" s="76"/>
-      <c r="O98" s="76"/>
-      <c r="P98" s="76"/>
-      <c r="Q98" s="76"/>
-      <c r="R98" s="76"/>
-      <c r="S98" s="76"/>
-      <c r="T98" s="76"/>
-      <c r="U98" s="76"/>
-      <c r="V98" s="76"/>
-      <c r="W98" s="76"/>
-      <c r="X98" s="76"/>
-      <c r="Y98" s="76"/>
-      <c r="Z98" s="76"/>
+      <c r="A98" s="87"/>
+      <c r="B98" s="87"/>
+      <c r="C98" s="87"/>
+      <c r="D98" s="87"/>
+      <c r="E98" s="89"/>
+      <c r="F98" s="87"/>
+      <c r="G98" s="87"/>
+      <c r="H98" s="87"/>
+      <c r="I98" s="87"/>
+      <c r="J98" s="87"/>
+      <c r="K98" s="87"/>
+      <c r="L98" s="87"/>
+      <c r="M98" s="87"/>
+      <c r="N98" s="87"/>
+      <c r="O98" s="87"/>
+      <c r="P98" s="87"/>
+      <c r="Q98" s="87"/>
+      <c r="R98" s="87"/>
+      <c r="S98" s="87"/>
+      <c r="T98" s="87"/>
+      <c r="U98" s="87"/>
+      <c r="V98" s="87"/>
+      <c r="W98" s="87"/>
+      <c r="X98" s="87"/>
+      <c r="Y98" s="87"/>
+      <c r="Z98" s="87"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="76"/>
-      <c r="B99" s="76"/>
-      <c r="C99" s="76"/>
-      <c r="D99" s="76"/>
-      <c r="E99" s="78"/>
-      <c r="F99" s="76"/>
-      <c r="G99" s="76"/>
-      <c r="H99" s="76"/>
-      <c r="I99" s="76"/>
-      <c r="J99" s="76"/>
-      <c r="K99" s="76"/>
-      <c r="L99" s="76"/>
-      <c r="M99" s="76"/>
-      <c r="N99" s="76"/>
-      <c r="O99" s="76"/>
-      <c r="P99" s="76"/>
-      <c r="Q99" s="76"/>
-      <c r="R99" s="76"/>
-      <c r="S99" s="76"/>
-      <c r="T99" s="76"/>
-      <c r="U99" s="76"/>
-      <c r="V99" s="76"/>
-      <c r="W99" s="76"/>
-      <c r="X99" s="76"/>
-      <c r="Y99" s="76"/>
-      <c r="Z99" s="76"/>
+      <c r="A99" s="87"/>
+      <c r="B99" s="87"/>
+      <c r="C99" s="87"/>
+      <c r="D99" s="87"/>
+      <c r="E99" s="89"/>
+      <c r="F99" s="87"/>
+      <c r="G99" s="87"/>
+      <c r="H99" s="87"/>
+      <c r="I99" s="87"/>
+      <c r="J99" s="87"/>
+      <c r="K99" s="87"/>
+      <c r="L99" s="87"/>
+      <c r="M99" s="87"/>
+      <c r="N99" s="87"/>
+      <c r="O99" s="87"/>
+      <c r="P99" s="87"/>
+      <c r="Q99" s="87"/>
+      <c r="R99" s="87"/>
+      <c r="S99" s="87"/>
+      <c r="T99" s="87"/>
+      <c r="U99" s="87"/>
+      <c r="V99" s="87"/>
+      <c r="W99" s="87"/>
+      <c r="X99" s="87"/>
+      <c r="Y99" s="87"/>
+      <c r="Z99" s="87"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="76"/>
-      <c r="B100" s="76"/>
-      <c r="C100" s="76"/>
-      <c r="D100" s="76"/>
-      <c r="E100" s="78"/>
-      <c r="F100" s="76"/>
-      <c r="G100" s="76"/>
-      <c r="H100" s="76"/>
-      <c r="I100" s="76"/>
-      <c r="J100" s="76"/>
-      <c r="K100" s="76"/>
-      <c r="L100" s="76"/>
-      <c r="M100" s="76"/>
-      <c r="N100" s="76"/>
-      <c r="O100" s="76"/>
-      <c r="P100" s="76"/>
-      <c r="Q100" s="76"/>
-      <c r="R100" s="76"/>
-      <c r="S100" s="76"/>
-      <c r="T100" s="76"/>
-      <c r="U100" s="76"/>
-      <c r="V100" s="76"/>
-      <c r="W100" s="76"/>
-      <c r="X100" s="76"/>
-      <c r="Y100" s="76"/>
-      <c r="Z100" s="76"/>
+      <c r="A100" s="87"/>
+      <c r="B100" s="87"/>
+      <c r="C100" s="87"/>
+      <c r="D100" s="87"/>
+      <c r="E100" s="89"/>
+      <c r="F100" s="87"/>
+      <c r="G100" s="87"/>
+      <c r="H100" s="87"/>
+      <c r="I100" s="87"/>
+      <c r="J100" s="87"/>
+      <c r="K100" s="87"/>
+      <c r="L100" s="87"/>
+      <c r="M100" s="87"/>
+      <c r="N100" s="87"/>
+      <c r="O100" s="87"/>
+      <c r="P100" s="87"/>
+      <c r="Q100" s="87"/>
+      <c r="R100" s="87"/>
+      <c r="S100" s="87"/>
+      <c r="T100" s="87"/>
+      <c r="U100" s="87"/>
+      <c r="V100" s="87"/>
+      <c r="W100" s="87"/>
+      <c r="X100" s="87"/>
+      <c r="Y100" s="87"/>
+      <c r="Z100" s="87"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="76"/>
-      <c r="B101" s="76"/>
-      <c r="C101" s="76"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="76"/>
-      <c r="G101" s="76"/>
-      <c r="H101" s="76"/>
-      <c r="I101" s="76"/>
-      <c r="J101" s="76"/>
-      <c r="K101" s="76"/>
-      <c r="L101" s="76"/>
-      <c r="M101" s="76"/>
-      <c r="N101" s="76"/>
-      <c r="O101" s="76"/>
-      <c r="P101" s="76"/>
-      <c r="Q101" s="76"/>
-      <c r="R101" s="76"/>
-      <c r="S101" s="76"/>
-      <c r="T101" s="76"/>
-      <c r="U101" s="76"/>
-      <c r="V101" s="76"/>
-      <c r="W101" s="76"/>
-      <c r="X101" s="76"/>
-      <c r="Y101" s="76"/>
-      <c r="Z101" s="76"/>
+      <c r="A101" s="87"/>
+      <c r="B101" s="87"/>
+      <c r="C101" s="87"/>
+      <c r="D101" s="87"/>
+      <c r="E101" s="89"/>
+      <c r="F101" s="87"/>
+      <c r="G101" s="87"/>
+      <c r="H101" s="87"/>
+      <c r="I101" s="87"/>
+      <c r="J101" s="87"/>
+      <c r="K101" s="87"/>
+      <c r="L101" s="87"/>
+      <c r="M101" s="87"/>
+      <c r="N101" s="87"/>
+      <c r="O101" s="87"/>
+      <c r="P101" s="87"/>
+      <c r="Q101" s="87"/>
+      <c r="R101" s="87"/>
+      <c r="S101" s="87"/>
+      <c r="T101" s="87"/>
+      <c r="U101" s="87"/>
+      <c r="V101" s="87"/>
+      <c r="W101" s="87"/>
+      <c r="X101" s="87"/>
+      <c r="Y101" s="87"/>
+      <c r="Z101" s="87"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="76"/>
-      <c r="B102" s="76"/>
-      <c r="C102" s="76"/>
-      <c r="D102" s="76"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="76"/>
-      <c r="G102" s="76"/>
-      <c r="H102" s="76"/>
-      <c r="I102" s="76"/>
-      <c r="J102" s="76"/>
-      <c r="K102" s="76"/>
-      <c r="L102" s="76"/>
-      <c r="M102" s="76"/>
-      <c r="N102" s="76"/>
-      <c r="O102" s="76"/>
-      <c r="P102" s="76"/>
-      <c r="Q102" s="76"/>
-      <c r="R102" s="76"/>
-      <c r="S102" s="76"/>
-      <c r="T102" s="76"/>
-      <c r="U102" s="76"/>
-      <c r="V102" s="76"/>
-      <c r="W102" s="76"/>
-      <c r="X102" s="76"/>
-      <c r="Y102" s="76"/>
-      <c r="Z102" s="76"/>
+      <c r="A102" s="87"/>
+      <c r="B102" s="87"/>
+      <c r="C102" s="87"/>
+      <c r="D102" s="87"/>
+      <c r="E102" s="89"/>
+      <c r="F102" s="87"/>
+      <c r="G102" s="87"/>
+      <c r="H102" s="87"/>
+      <c r="I102" s="87"/>
+      <c r="J102" s="87"/>
+      <c r="K102" s="87"/>
+      <c r="L102" s="87"/>
+      <c r="M102" s="87"/>
+      <c r="N102" s="87"/>
+      <c r="O102" s="87"/>
+      <c r="P102" s="87"/>
+      <c r="Q102" s="87"/>
+      <c r="R102" s="87"/>
+      <c r="S102" s="87"/>
+      <c r="T102" s="87"/>
+      <c r="U102" s="87"/>
+      <c r="V102" s="87"/>
+      <c r="W102" s="87"/>
+      <c r="X102" s="87"/>
+      <c r="Y102" s="87"/>
+      <c r="Z102" s="87"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
@@ -14858,25 +14863,25 @@
       <c r="E103" s="3"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
-      <c r="H103" s="76"/>
-      <c r="I103" s="76"/>
-      <c r="J103" s="76"/>
-      <c r="K103" s="76"/>
-      <c r="L103" s="76"/>
-      <c r="M103" s="76"/>
-      <c r="N103" s="76"/>
-      <c r="O103" s="76"/>
-      <c r="P103" s="76"/>
-      <c r="Q103" s="76"/>
-      <c r="R103" s="76"/>
-      <c r="S103" s="76"/>
-      <c r="T103" s="76"/>
-      <c r="U103" s="76"/>
-      <c r="V103" s="76"/>
-      <c r="W103" s="76"/>
-      <c r="X103" s="76"/>
-      <c r="Y103" s="76"/>
-      <c r="Z103" s="76"/>
+      <c r="H103" s="87"/>
+      <c r="I103" s="87"/>
+      <c r="J103" s="87"/>
+      <c r="K103" s="87"/>
+      <c r="L103" s="87"/>
+      <c r="M103" s="87"/>
+      <c r="N103" s="87"/>
+      <c r="O103" s="87"/>
+      <c r="P103" s="87"/>
+      <c r="Q103" s="87"/>
+      <c r="R103" s="87"/>
+      <c r="S103" s="87"/>
+      <c r="T103" s="87"/>
+      <c r="U103" s="87"/>
+      <c r="V103" s="87"/>
+      <c r="W103" s="87"/>
+      <c r="X103" s="87"/>
+      <c r="Y103" s="87"/>
+      <c r="Z103" s="87"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
